--- a/Data/ModelResponse/3_MAIA-like/evaluation/3_MAIA-like_evaluation_summary.xlsx
+++ b/Data/ModelResponse/3_MAIA-like/evaluation/3_MAIA-like_evaluation_summary.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U2"/>
+  <dimension ref="A1:R2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -428,102 +428,87 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>n_samples</t>
+          <t>total_examples</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>valid_predictions</t>
+          <t>valid_answers</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>invalid_predictions</t>
+          <t>invalid_answers</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>empty_raw_outputs</t>
+          <t>empty_answers</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Accuracy</t>
+          <t>correct_answers</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Accuracy_valid_only</t>
+          <t>overall_accuracy</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Support_0</t>
+          <t>valid_only_accuracy</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Predicted_as_0</t>
+          <t>precision_label_0</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>Precision_0</t>
+          <t>recall_label_0</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>Recall_0</t>
+          <t>f1_label_0</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>F1_0</t>
+          <t>precision_label_1</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>Support_1</t>
+          <t>recall_label_1</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>Predicted_as_1</t>
+          <t>f1_label_1</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>Precision_1</t>
+          <t>true_0_pred_0</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>Recall_1</t>
+          <t>true_0_pred_1</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>F1_1</t>
+          <t>true_1_pred_0</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>actual_0_pred_0</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>actual_0_pred_1</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>actual_1_pred_0</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>actual_1_pred_1</t>
+          <t>true_1_pred_1</t>
         </is>
       </c>
     </row>
@@ -546,51 +531,42 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.74625</v>
+        <v>14328</v>
       </c>
       <c r="G2" t="n">
         <v>0.74625</v>
       </c>
       <c r="H2" t="n">
-        <v>9554</v>
+        <v>0.74625</v>
       </c>
       <c r="I2" t="n">
-        <v>12732</v>
+        <v>0.6838674206723218</v>
       </c>
       <c r="J2" t="n">
-        <v>0.6838674206723218</v>
+        <v>0.9113460330751517</v>
       </c>
       <c r="K2" t="n">
-        <v>0.9113460330751517</v>
+        <v>0.7813874181100242</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7813874181100242</v>
+        <v>0.8690476190476191</v>
       </c>
       <c r="M2" t="n">
-        <v>9646</v>
+        <v>0.5827285921625545</v>
       </c>
       <c r="N2" t="n">
-        <v>6468</v>
+        <v>0.6976542137271937</v>
       </c>
       <c r="O2" t="n">
-        <v>0.8690476190476191</v>
+        <v>8707</v>
       </c>
       <c r="P2" t="n">
-        <v>0.5827285921625545</v>
+        <v>847</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.6976542137271937</v>
+        <v>4025</v>
       </c>
       <c r="R2" t="n">
-        <v>8707</v>
-      </c>
-      <c r="S2" t="n">
-        <v>847</v>
-      </c>
-      <c r="T2" t="n">
-        <v>4025</v>
-      </c>
-      <c r="U2" t="n">
         <v>5621</v>
       </c>
     </row>
@@ -605,7 +581,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U14"/>
+  <dimension ref="A1:R14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -616,102 +592,87 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>n_samples</t>
+          <t>total_examples</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>valid_predictions</t>
+          <t>valid_answers</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>invalid_predictions</t>
+          <t>invalid_answers</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>empty_raw_outputs</t>
+          <t>empty_answers</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Accuracy</t>
+          <t>correct_answers</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Accuracy_valid_only</t>
+          <t>overall_accuracy</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Support_0</t>
+          <t>valid_only_accuracy</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Predicted_as_0</t>
+          <t>precision_label_0</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>Precision_0</t>
+          <t>recall_label_0</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>Recall_0</t>
+          <t>f1_label_0</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>F1_0</t>
+          <t>precision_label_1</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>Support_1</t>
+          <t>recall_label_1</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>Predicted_as_1</t>
+          <t>f1_label_1</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>Precision_1</t>
+          <t>true_0_pred_0</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>Recall_1</t>
+          <t>true_0_pred_1</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>F1_1</t>
+          <t>true_1_pred_0</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>actual_0_pred_0</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>actual_0_pred_1</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>actual_1_pred_0</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>actual_1_pred_1</t>
+          <t>true_1_pred_1</t>
         </is>
       </c>
     </row>
@@ -734,51 +695,42 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.79375</v>
+        <v>635</v>
       </c>
       <c r="G2" t="n">
         <v>0.79375</v>
       </c>
       <c r="H2" t="n">
-        <v>387</v>
+        <v>0.79375</v>
       </c>
       <c r="I2" t="n">
-        <v>526</v>
+        <v>0.7110266159695817</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7110266159695817</v>
+        <v>0.9664082687338501</v>
       </c>
       <c r="K2" t="n">
-        <v>0.9664082687338501</v>
+        <v>0.819277108433735</v>
       </c>
       <c r="L2" t="n">
-        <v>0.819277108433735</v>
+        <v>0.9525547445255474</v>
       </c>
       <c r="M2" t="n">
-        <v>413</v>
+        <v>0.6319612590799032</v>
       </c>
       <c r="N2" t="n">
-        <v>274</v>
+        <v>0.759825327510917</v>
       </c>
       <c r="O2" t="n">
-        <v>0.9525547445255474</v>
+        <v>374</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6319612590799032</v>
+        <v>13</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.759825327510917</v>
+        <v>152</v>
       </c>
       <c r="R2" t="n">
-        <v>374</v>
-      </c>
-      <c r="S2" t="n">
-        <v>13</v>
-      </c>
-      <c r="T2" t="n">
-        <v>152</v>
-      </c>
-      <c r="U2" t="n">
         <v>261</v>
       </c>
     </row>
@@ -801,51 +753,42 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0.81625</v>
+        <v>653</v>
       </c>
       <c r="G3" t="n">
         <v>0.81625</v>
       </c>
       <c r="H3" t="n">
-        <v>404</v>
+        <v>0.81625</v>
       </c>
       <c r="I3" t="n">
-        <v>497</v>
+        <v>0.7585513078470825</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7585513078470825</v>
+        <v>0.9331683168316832</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9331683168316832</v>
+        <v>0.8368479467258603</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8368479467258603</v>
+        <v>0.9108910891089109</v>
       </c>
       <c r="M3" t="n">
-        <v>396</v>
+        <v>0.696969696969697</v>
       </c>
       <c r="N3" t="n">
-        <v>303</v>
+        <v>0.7896995708154506</v>
       </c>
       <c r="O3" t="n">
-        <v>0.9108910891089109</v>
+        <v>377</v>
       </c>
       <c r="P3" t="n">
-        <v>0.696969696969697</v>
+        <v>27</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.7896995708154506</v>
+        <v>120</v>
       </c>
       <c r="R3" t="n">
-        <v>377</v>
-      </c>
-      <c r="S3" t="n">
-        <v>27</v>
-      </c>
-      <c r="T3" t="n">
-        <v>120</v>
-      </c>
-      <c r="U3" t="n">
         <v>276</v>
       </c>
     </row>
@@ -868,51 +811,42 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0.64375</v>
+        <v>1030</v>
       </c>
       <c r="G4" t="n">
         <v>0.64375</v>
       </c>
       <c r="H4" t="n">
-        <v>821</v>
+        <v>0.64375</v>
       </c>
       <c r="I4" t="n">
-        <v>1079</v>
+        <v>0.6163113994439295</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6163113994439295</v>
+        <v>0.8099878197320342</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8099878197320342</v>
+        <v>0.7</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7</v>
+        <v>0.7005758157389635</v>
       </c>
       <c r="M4" t="n">
-        <v>779</v>
+        <v>0.4685494223363286</v>
       </c>
       <c r="N4" t="n">
-        <v>521</v>
+        <v>0.5615384615384617</v>
       </c>
       <c r="O4" t="n">
-        <v>0.7005758157389635</v>
+        <v>665</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4685494223363286</v>
+        <v>156</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.5615384615384617</v>
+        <v>414</v>
       </c>
       <c r="R4" t="n">
-        <v>665</v>
-      </c>
-      <c r="S4" t="n">
-        <v>156</v>
-      </c>
-      <c r="T4" t="n">
-        <v>414</v>
-      </c>
-      <c r="U4" t="n">
         <v>365</v>
       </c>
     </row>
@@ -935,51 +869,42 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0.75125</v>
+        <v>1202</v>
       </c>
       <c r="G5" t="n">
         <v>0.75125</v>
       </c>
       <c r="H5" t="n">
-        <v>805</v>
+        <v>0.75125</v>
       </c>
       <c r="I5" t="n">
-        <v>1051</v>
+        <v>0.6936251189343482</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6936251189343482</v>
+        <v>0.9055900621118013</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9055900621118013</v>
+        <v>0.7855603448275862</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7855603448275862</v>
+        <v>0.8615664845173042</v>
       </c>
       <c r="M5" t="n">
-        <v>795</v>
+        <v>0.5949685534591195</v>
       </c>
       <c r="N5" t="n">
-        <v>549</v>
+        <v>0.7038690476190477</v>
       </c>
       <c r="O5" t="n">
-        <v>0.8615664845173042</v>
+        <v>729</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5949685534591195</v>
+        <v>76</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.7038690476190477</v>
+        <v>322</v>
       </c>
       <c r="R5" t="n">
-        <v>729</v>
-      </c>
-      <c r="S5" t="n">
-        <v>76</v>
-      </c>
-      <c r="T5" t="n">
-        <v>322</v>
-      </c>
-      <c r="U5" t="n">
         <v>473</v>
       </c>
     </row>
@@ -1002,51 +927,42 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0.811875</v>
+        <v>1299</v>
       </c>
       <c r="G6" t="n">
         <v>0.811875</v>
       </c>
       <c r="H6" t="n">
-        <v>821</v>
+        <v>0.811875</v>
       </c>
       <c r="I6" t="n">
-        <v>1010</v>
+        <v>0.7574257425742574</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7574257425742574</v>
+        <v>0.9317904993909866</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9317904993909866</v>
+        <v>0.8356089568541781</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8356089568541781</v>
+        <v>0.9050847457627119</v>
       </c>
       <c r="M6" t="n">
-        <v>779</v>
+        <v>0.6854942233632862</v>
       </c>
       <c r="N6" t="n">
-        <v>590</v>
+        <v>0.7801314828341855</v>
       </c>
       <c r="O6" t="n">
-        <v>0.9050847457627119</v>
+        <v>765</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6854942233632862</v>
+        <v>56</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.7801314828341855</v>
+        <v>245</v>
       </c>
       <c r="R6" t="n">
-        <v>765</v>
-      </c>
-      <c r="S6" t="n">
-        <v>56</v>
-      </c>
-      <c r="T6" t="n">
-        <v>245</v>
-      </c>
-      <c r="U6" t="n">
         <v>534</v>
       </c>
     </row>
@@ -1069,51 +985,42 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0.733125</v>
+        <v>1173</v>
       </c>
       <c r="G7" t="n">
         <v>0.733125</v>
       </c>
       <c r="H7" t="n">
-        <v>740</v>
+        <v>0.733125</v>
       </c>
       <c r="I7" t="n">
-        <v>1091</v>
+        <v>0.6434463794683777</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6434463794683777</v>
+        <v>0.9486486486486486</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9486486486486486</v>
+        <v>0.7667941015838341</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7667941015838341</v>
+        <v>0.925343811394892</v>
       </c>
       <c r="M7" t="n">
-        <v>860</v>
+        <v>0.5476744186046512</v>
       </c>
       <c r="N7" t="n">
-        <v>509</v>
+        <v>0.6880934989043097</v>
       </c>
       <c r="O7" t="n">
-        <v>0.925343811394892</v>
+        <v>702</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5476744186046512</v>
+        <v>38</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.6880934989043097</v>
+        <v>389</v>
       </c>
       <c r="R7" t="n">
-        <v>702</v>
-      </c>
-      <c r="S7" t="n">
-        <v>38</v>
-      </c>
-      <c r="T7" t="n">
-        <v>389</v>
-      </c>
-      <c r="U7" t="n">
         <v>471</v>
       </c>
     </row>
@@ -1136,51 +1043,42 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0.876875</v>
+        <v>1403</v>
       </c>
       <c r="G8" t="n">
         <v>0.876875</v>
       </c>
       <c r="H8" t="n">
-        <v>769</v>
+        <v>0.876875</v>
       </c>
       <c r="I8" t="n">
-        <v>864</v>
+        <v>0.8310185185185185</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8310185185185185</v>
+        <v>0.9336801040312094</v>
       </c>
       <c r="K8" t="n">
-        <v>0.9336801040312094</v>
+        <v>0.8793631353337417</v>
       </c>
       <c r="L8" t="n">
-        <v>0.8793631353337417</v>
+        <v>0.9307065217391305</v>
       </c>
       <c r="M8" t="n">
-        <v>831</v>
+        <v>0.8243080625752106</v>
       </c>
       <c r="N8" t="n">
-        <v>736</v>
+        <v>0.874282067645182</v>
       </c>
       <c r="O8" t="n">
-        <v>0.9307065217391305</v>
+        <v>718</v>
       </c>
       <c r="P8" t="n">
-        <v>0.8243080625752106</v>
+        <v>51</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.874282067645182</v>
+        <v>146</v>
       </c>
       <c r="R8" t="n">
-        <v>718</v>
-      </c>
-      <c r="S8" t="n">
-        <v>51</v>
-      </c>
-      <c r="T8" t="n">
-        <v>146</v>
-      </c>
-      <c r="U8" t="n">
         <v>685</v>
       </c>
     </row>
@@ -1203,51 +1101,42 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0.66875</v>
+        <v>1070</v>
       </c>
       <c r="G9" t="n">
         <v>0.66875</v>
       </c>
       <c r="H9" t="n">
-        <v>822</v>
+        <v>0.66875</v>
       </c>
       <c r="I9" t="n">
-        <v>1268</v>
+        <v>0.6151419558359621</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6151419558359621</v>
+        <v>0.948905109489051</v>
       </c>
       <c r="K9" t="n">
-        <v>0.948905109489051</v>
+        <v>0.7464114832535884</v>
       </c>
       <c r="L9" t="n">
-        <v>0.7464114832535884</v>
+        <v>0.8734939759036144</v>
       </c>
       <c r="M9" t="n">
-        <v>778</v>
+        <v>0.3727506426735219</v>
       </c>
       <c r="N9" t="n">
-        <v>332</v>
+        <v>0.5225225225225226</v>
       </c>
       <c r="O9" t="n">
-        <v>0.8734939759036144</v>
+        <v>780</v>
       </c>
       <c r="P9" t="n">
-        <v>0.3727506426735219</v>
+        <v>42</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.5225225225225226</v>
+        <v>488</v>
       </c>
       <c r="R9" t="n">
-        <v>780</v>
-      </c>
-      <c r="S9" t="n">
-        <v>42</v>
-      </c>
-      <c r="T9" t="n">
-        <v>488</v>
-      </c>
-      <c r="U9" t="n">
         <v>290</v>
       </c>
     </row>
@@ -1270,51 +1159,42 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8175</v>
+        <v>1308</v>
       </c>
       <c r="G10" t="n">
         <v>0.8175</v>
       </c>
       <c r="H10" t="n">
-        <v>804</v>
+        <v>0.8175</v>
       </c>
       <c r="I10" t="n">
-        <v>1046</v>
+        <v>0.7447418738049714</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7447418738049714</v>
+        <v>0.9689054726368159</v>
       </c>
       <c r="K10" t="n">
-        <v>0.9689054726368159</v>
+        <v>0.8421621621621622</v>
       </c>
       <c r="L10" t="n">
-        <v>0.8421621621621622</v>
+        <v>0.9548736462093863</v>
       </c>
       <c r="M10" t="n">
-        <v>796</v>
+        <v>0.664572864321608</v>
       </c>
       <c r="N10" t="n">
-        <v>554</v>
+        <v>0.7837037037037037</v>
       </c>
       <c r="O10" t="n">
-        <v>0.9548736462093863</v>
+        <v>779</v>
       </c>
       <c r="P10" t="n">
-        <v>0.664572864321608</v>
+        <v>25</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.7837037037037037</v>
+        <v>267</v>
       </c>
       <c r="R10" t="n">
-        <v>779</v>
-      </c>
-      <c r="S10" t="n">
-        <v>25</v>
-      </c>
-      <c r="T10" t="n">
-        <v>267</v>
-      </c>
-      <c r="U10" t="n">
         <v>529</v>
       </c>
     </row>
@@ -1337,51 +1217,42 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6899999999999999</v>
+        <v>1104</v>
       </c>
       <c r="G11" t="n">
         <v>0.6899999999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>812</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>1100</v>
+        <v>0.6436363636363637</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6436363636363637</v>
+        <v>0.8719211822660099</v>
       </c>
       <c r="K11" t="n">
-        <v>0.8719211822660099</v>
+        <v>0.7405857740585774</v>
       </c>
       <c r="L11" t="n">
-        <v>0.7405857740585774</v>
+        <v>0.792</v>
       </c>
       <c r="M11" t="n">
-        <v>788</v>
+        <v>0.5025380710659898</v>
       </c>
       <c r="N11" t="n">
-        <v>500</v>
+        <v>0.6149068322981367</v>
       </c>
       <c r="O11" t="n">
-        <v>0.792</v>
+        <v>708</v>
       </c>
       <c r="P11" t="n">
-        <v>0.5025380710659898</v>
+        <v>104</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.6149068322981367</v>
+        <v>392</v>
       </c>
       <c r="R11" t="n">
-        <v>708</v>
-      </c>
-      <c r="S11" t="n">
-        <v>104</v>
-      </c>
-      <c r="T11" t="n">
-        <v>392</v>
-      </c>
-      <c r="U11" t="n">
         <v>396</v>
       </c>
     </row>
@@ -1404,51 +1275,42 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0.87</v>
+        <v>1392</v>
       </c>
       <c r="G12" t="n">
         <v>0.87</v>
       </c>
       <c r="H12" t="n">
-        <v>788</v>
+        <v>0.87</v>
       </c>
       <c r="I12" t="n">
-        <v>798</v>
+        <v>0.8634085213032582</v>
       </c>
       <c r="J12" t="n">
-        <v>0.8634085213032582</v>
+        <v>0.8743654822335025</v>
       </c>
       <c r="K12" t="n">
-        <v>0.8743654822335025</v>
+        <v>0.8688524590163935</v>
       </c>
       <c r="L12" t="n">
-        <v>0.8688524590163935</v>
+        <v>0.8765586034912718</v>
       </c>
       <c r="M12" t="n">
-        <v>812</v>
+        <v>0.8657635467980296</v>
       </c>
       <c r="N12" t="n">
-        <v>802</v>
+        <v>0.8711276332094177</v>
       </c>
       <c r="O12" t="n">
-        <v>0.8765586034912718</v>
+        <v>689</v>
       </c>
       <c r="P12" t="n">
-        <v>0.8657635467980296</v>
+        <v>99</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.8711276332094177</v>
+        <v>109</v>
       </c>
       <c r="R12" t="n">
-        <v>689</v>
-      </c>
-      <c r="S12" t="n">
-        <v>99</v>
-      </c>
-      <c r="T12" t="n">
-        <v>109</v>
-      </c>
-      <c r="U12" t="n">
         <v>703</v>
       </c>
     </row>
@@ -1471,51 +1333,42 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0.628125</v>
+        <v>1005</v>
       </c>
       <c r="G13" t="n">
         <v>0.628125</v>
       </c>
       <c r="H13" t="n">
-        <v>813</v>
+        <v>0.628125</v>
       </c>
       <c r="I13" t="n">
-        <v>1174</v>
+        <v>0.5928449744463373</v>
       </c>
       <c r="J13" t="n">
-        <v>0.5928449744463373</v>
+        <v>0.8560885608856088</v>
       </c>
       <c r="K13" t="n">
-        <v>0.8560885608856088</v>
+        <v>0.7005535983895319</v>
       </c>
       <c r="L13" t="n">
-        <v>0.7005535983895319</v>
+        <v>0.7253521126760564</v>
       </c>
       <c r="M13" t="n">
-        <v>787</v>
+        <v>0.3926302414231258</v>
       </c>
       <c r="N13" t="n">
-        <v>426</v>
+        <v>0.5094806265457543</v>
       </c>
       <c r="O13" t="n">
-        <v>0.7253521126760564</v>
+        <v>696</v>
       </c>
       <c r="P13" t="n">
-        <v>0.3926302414231258</v>
+        <v>117</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.5094806265457543</v>
+        <v>478</v>
       </c>
       <c r="R13" t="n">
-        <v>696</v>
-      </c>
-      <c r="S13" t="n">
-        <v>117</v>
-      </c>
-      <c r="T13" t="n">
-        <v>478</v>
-      </c>
-      <c r="U13" t="n">
         <v>309</v>
       </c>
     </row>
@@ -1538,51 +1391,42 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>0.6587499999999999</v>
+        <v>1054</v>
       </c>
       <c r="G14" t="n">
         <v>0.6587499999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>768</v>
+        <v>0.6587499999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>1228</v>
+        <v>0.5903908794788274</v>
       </c>
       <c r="J14" t="n">
-        <v>0.5903908794788274</v>
+        <v>0.9440104166666666</v>
       </c>
       <c r="K14" t="n">
-        <v>0.9440104166666666</v>
+        <v>0.7264529058116234</v>
       </c>
       <c r="L14" t="n">
-        <v>0.7264529058116234</v>
+        <v>0.8844086021505376</v>
       </c>
       <c r="M14" t="n">
-        <v>832</v>
+        <v>0.3954326923076923</v>
       </c>
       <c r="N14" t="n">
-        <v>372</v>
+        <v>0.5465116279069766</v>
       </c>
       <c r="O14" t="n">
-        <v>0.8844086021505376</v>
+        <v>725</v>
       </c>
       <c r="P14" t="n">
-        <v>0.3954326923076923</v>
+        <v>43</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.5465116279069766</v>
+        <v>503</v>
       </c>
       <c r="R14" t="n">
-        <v>725</v>
-      </c>
-      <c r="S14" t="n">
-        <v>43</v>
-      </c>
-      <c r="T14" t="n">
-        <v>503</v>
-      </c>
-      <c r="U14" t="n">
         <v>329</v>
       </c>
     </row>
@@ -1597,7 +1441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U101"/>
+  <dimension ref="A1:R101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1608,102 +1452,87 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>n_samples</t>
+          <t>total_examples</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>valid_predictions</t>
+          <t>valid_answers</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>invalid_predictions</t>
+          <t>invalid_answers</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>empty_raw_outputs</t>
+          <t>empty_answers</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Accuracy</t>
+          <t>correct_answers</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Accuracy_valid_only</t>
+          <t>overall_accuracy</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Support_0</t>
+          <t>valid_only_accuracy</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Predicted_as_0</t>
+          <t>precision_label_0</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>Precision_0</t>
+          <t>recall_label_0</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>Recall_0</t>
+          <t>f1_label_0</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>F1_0</t>
+          <t>precision_label_1</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>Support_1</t>
+          <t>recall_label_1</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>Predicted_as_1</t>
+          <t>f1_label_1</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>Precision_1</t>
+          <t>true_0_pred_0</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>Recall_1</t>
+          <t>true_0_pred_1</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>F1_1</t>
+          <t>true_1_pred_0</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>actual_0_pred_0</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>actual_0_pred_1</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>actual_1_pred_0</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>actual_1_pred_1</t>
+          <t>true_1_pred_1</t>
         </is>
       </c>
     </row>
@@ -1726,51 +1555,42 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7604166666666666</v>
+        <v>146</v>
       </c>
       <c r="G2" t="n">
         <v>0.7604166666666666</v>
       </c>
       <c r="H2" t="n">
-        <v>89</v>
+        <v>0.7604166666666666</v>
       </c>
       <c r="I2" t="n">
-        <v>117</v>
+        <v>0.6837606837606838</v>
       </c>
       <c r="J2" t="n">
-        <v>0.6837606837606838</v>
+        <v>0.898876404494382</v>
       </c>
       <c r="K2" t="n">
-        <v>0.898876404494382</v>
+        <v>0.7766990291262137</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7766990291262137</v>
+        <v>0.88</v>
       </c>
       <c r="M2" t="n">
-        <v>103</v>
+        <v>0.6407766990291263</v>
       </c>
       <c r="N2" t="n">
-        <v>75</v>
+        <v>0.7415730337078652</v>
       </c>
       <c r="O2" t="n">
-        <v>0.88</v>
+        <v>80</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6407766990291263</v>
+        <v>9</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.7415730337078652</v>
+        <v>37</v>
       </c>
       <c r="R2" t="n">
-        <v>80</v>
-      </c>
-      <c r="S2" t="n">
-        <v>9</v>
-      </c>
-      <c r="T2" t="n">
-        <v>37</v>
-      </c>
-      <c r="U2" t="n">
         <v>66</v>
       </c>
     </row>
@@ -1793,51 +1613,42 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6822916666666666</v>
+        <v>131</v>
       </c>
       <c r="G3" t="n">
         <v>0.6822916666666666</v>
       </c>
       <c r="H3" t="n">
-        <v>93</v>
+        <v>0.6822916666666666</v>
       </c>
       <c r="I3" t="n">
-        <v>130</v>
+        <v>0.6230769230769231</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6230769230769231</v>
+        <v>0.8709677419354839</v>
       </c>
       <c r="K3" t="n">
-        <v>0.8709677419354839</v>
+        <v>0.7264573991031389</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7264573991031389</v>
+        <v>0.8064516129032258</v>
       </c>
       <c r="M3" t="n">
-        <v>99</v>
+        <v>0.5050505050505051</v>
       </c>
       <c r="N3" t="n">
-        <v>62</v>
+        <v>0.6211180124223603</v>
       </c>
       <c r="O3" t="n">
-        <v>0.8064516129032258</v>
+        <v>81</v>
       </c>
       <c r="P3" t="n">
-        <v>0.5050505050505051</v>
+        <v>12</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.6211180124223603</v>
+        <v>49</v>
       </c>
       <c r="R3" t="n">
-        <v>81</v>
-      </c>
-      <c r="S3" t="n">
-        <v>12</v>
-      </c>
-      <c r="T3" t="n">
-        <v>49</v>
-      </c>
-      <c r="U3" t="n">
         <v>50</v>
       </c>
     </row>
@@ -1860,51 +1671,42 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8385416666666666</v>
+        <v>161</v>
       </c>
       <c r="G4" t="n">
         <v>0.8385416666666666</v>
       </c>
       <c r="H4" t="n">
-        <v>110</v>
+        <v>0.8385416666666666</v>
       </c>
       <c r="I4" t="n">
-        <v>133</v>
+        <v>0.7969924812030075</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7969924812030075</v>
+        <v>0.9636363636363636</v>
       </c>
       <c r="K4" t="n">
-        <v>0.9636363636363636</v>
+        <v>0.8724279835390947</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8724279835390947</v>
+        <v>0.9322033898305084</v>
       </c>
       <c r="M4" t="n">
-        <v>82</v>
+        <v>0.6707317073170732</v>
       </c>
       <c r="N4" t="n">
-        <v>59</v>
+        <v>0.7801418439716312</v>
       </c>
       <c r="O4" t="n">
-        <v>0.9322033898305084</v>
+        <v>106</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6707317073170732</v>
+        <v>4</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.7801418439716312</v>
+        <v>27</v>
       </c>
       <c r="R4" t="n">
-        <v>106</v>
-      </c>
-      <c r="S4" t="n">
-        <v>4</v>
-      </c>
-      <c r="T4" t="n">
-        <v>27</v>
-      </c>
-      <c r="U4" t="n">
         <v>55</v>
       </c>
     </row>
@@ -1927,51 +1729,42 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0.734375</v>
+        <v>141</v>
       </c>
       <c r="G5" t="n">
         <v>0.734375</v>
       </c>
       <c r="H5" t="n">
-        <v>97</v>
+        <v>0.734375</v>
       </c>
       <c r="I5" t="n">
-        <v>136</v>
+        <v>0.6691176470588235</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6691176470588235</v>
+        <v>0.9381443298969072</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9381443298969072</v>
+        <v>0.7811158798283261</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7811158798283261</v>
+        <v>0.8928571428571429</v>
       </c>
       <c r="M5" t="n">
-        <v>95</v>
+        <v>0.5263157894736842</v>
       </c>
       <c r="N5" t="n">
-        <v>56</v>
+        <v>0.662251655629139</v>
       </c>
       <c r="O5" t="n">
-        <v>0.8928571428571429</v>
+        <v>91</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5263157894736842</v>
+        <v>6</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.662251655629139</v>
+        <v>45</v>
       </c>
       <c r="R5" t="n">
-        <v>91</v>
-      </c>
-      <c r="S5" t="n">
-        <v>6</v>
-      </c>
-      <c r="T5" t="n">
-        <v>45</v>
-      </c>
-      <c r="U5" t="n">
         <v>50</v>
       </c>
     </row>
@@ -1994,51 +1787,42 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8229166666666666</v>
+        <v>158</v>
       </c>
       <c r="G6" t="n">
         <v>0.8229166666666666</v>
       </c>
       <c r="H6" t="n">
-        <v>103</v>
+        <v>0.8229166666666666</v>
       </c>
       <c r="I6" t="n">
-        <v>117</v>
+        <v>0.7948717948717948</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7948717948717948</v>
+        <v>0.9029126213592233</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9029126213592233</v>
+        <v>0.8454545454545455</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8454545454545455</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="M6" t="n">
-        <v>89</v>
+        <v>0.7303370786516854</v>
       </c>
       <c r="N6" t="n">
-        <v>75</v>
+        <v>0.7926829268292682</v>
       </c>
       <c r="O6" t="n">
-        <v>0.8666666666666667</v>
+        <v>93</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7303370786516854</v>
+        <v>10</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.7926829268292682</v>
+        <v>24</v>
       </c>
       <c r="R6" t="n">
-        <v>93</v>
-      </c>
-      <c r="S6" t="n">
-        <v>10</v>
-      </c>
-      <c r="T6" t="n">
-        <v>24</v>
-      </c>
-      <c r="U6" t="n">
         <v>65</v>
       </c>
     </row>
@@ -2061,51 +1845,42 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7708333333333334</v>
+        <v>148</v>
       </c>
       <c r="G7" t="n">
         <v>0.7708333333333334</v>
       </c>
       <c r="H7" t="n">
-        <v>94</v>
+        <v>0.7708333333333334</v>
       </c>
       <c r="I7" t="n">
-        <v>122</v>
+        <v>0.7049180327868853</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7049180327868853</v>
+        <v>0.9148936170212766</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9148936170212766</v>
+        <v>0.7962962962962963</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7962962962962963</v>
+        <v>0.8857142857142857</v>
       </c>
       <c r="M7" t="n">
-        <v>98</v>
+        <v>0.6326530612244898</v>
       </c>
       <c r="N7" t="n">
-        <v>70</v>
+        <v>0.7380952380952381</v>
       </c>
       <c r="O7" t="n">
-        <v>0.8857142857142857</v>
+        <v>86</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6326530612244898</v>
+        <v>8</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.7380952380952381</v>
+        <v>36</v>
       </c>
       <c r="R7" t="n">
-        <v>86</v>
-      </c>
-      <c r="S7" t="n">
-        <v>8</v>
-      </c>
-      <c r="T7" t="n">
-        <v>36</v>
-      </c>
-      <c r="U7" t="n">
         <v>62</v>
       </c>
     </row>
@@ -2128,51 +1903,42 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7708333333333334</v>
+        <v>148</v>
       </c>
       <c r="G8" t="n">
         <v>0.7708333333333334</v>
       </c>
       <c r="H8" t="n">
-        <v>92</v>
+        <v>0.7708333333333334</v>
       </c>
       <c r="I8" t="n">
-        <v>128</v>
+        <v>0.6875</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6875</v>
+        <v>0.9565217391304348</v>
       </c>
       <c r="K8" t="n">
-        <v>0.9565217391304348</v>
+        <v>0.8</v>
       </c>
       <c r="L8" t="n">
-        <v>0.8</v>
+        <v>0.9375</v>
       </c>
       <c r="M8" t="n">
-        <v>100</v>
+        <v>0.6</v>
       </c>
       <c r="N8" t="n">
-        <v>64</v>
+        <v>0.7317073170731707</v>
       </c>
       <c r="O8" t="n">
-        <v>0.9375</v>
+        <v>88</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6</v>
+        <v>4</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.7317073170731707</v>
+        <v>40</v>
       </c>
       <c r="R8" t="n">
-        <v>88</v>
-      </c>
-      <c r="S8" t="n">
-        <v>4</v>
-      </c>
-      <c r="T8" t="n">
-        <v>40</v>
-      </c>
-      <c r="U8" t="n">
         <v>60</v>
       </c>
     </row>
@@ -2195,51 +1961,42 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7916666666666666</v>
+        <v>152</v>
       </c>
       <c r="G9" t="n">
         <v>0.7916666666666666</v>
       </c>
       <c r="H9" t="n">
-        <v>104</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="I9" t="n">
-        <v>122</v>
+        <v>0.7622950819672131</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7622950819672131</v>
+        <v>0.8942307692307693</v>
       </c>
       <c r="K9" t="n">
-        <v>0.8942307692307693</v>
+        <v>0.8230088495575222</v>
       </c>
       <c r="L9" t="n">
-        <v>0.8230088495575222</v>
+        <v>0.8428571428571429</v>
       </c>
       <c r="M9" t="n">
-        <v>88</v>
+        <v>0.6704545454545454</v>
       </c>
       <c r="N9" t="n">
-        <v>70</v>
+        <v>0.7468354430379747</v>
       </c>
       <c r="O9" t="n">
-        <v>0.8428571428571429</v>
+        <v>93</v>
       </c>
       <c r="P9" t="n">
-        <v>0.6704545454545454</v>
+        <v>11</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.7468354430379747</v>
+        <v>29</v>
       </c>
       <c r="R9" t="n">
-        <v>93</v>
-      </c>
-      <c r="S9" t="n">
-        <v>11</v>
-      </c>
-      <c r="T9" t="n">
-        <v>29</v>
-      </c>
-      <c r="U9" t="n">
         <v>59</v>
       </c>
     </row>
@@ -2262,51 +2019,42 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6666666666666666</v>
+        <v>128</v>
       </c>
       <c r="G10" t="n">
         <v>0.6666666666666666</v>
       </c>
       <c r="H10" t="n">
-        <v>106</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="I10" t="n">
-        <v>158</v>
+        <v>0.6329113924050633</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6329113924050633</v>
+        <v>0.9433962264150944</v>
       </c>
       <c r="K10" t="n">
-        <v>0.9433962264150944</v>
+        <v>0.7575757575757577</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7575757575757577</v>
+        <v>0.8235294117647058</v>
       </c>
       <c r="M10" t="n">
-        <v>86</v>
+        <v>0.3255813953488372</v>
       </c>
       <c r="N10" t="n">
-        <v>34</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="O10" t="n">
-        <v>0.8235294117647058</v>
+        <v>100</v>
       </c>
       <c r="P10" t="n">
-        <v>0.3255813953488372</v>
+        <v>6</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.4666666666666667</v>
+        <v>58</v>
       </c>
       <c r="R10" t="n">
-        <v>100</v>
-      </c>
-      <c r="S10" t="n">
-        <v>6</v>
-      </c>
-      <c r="T10" t="n">
-        <v>58</v>
-      </c>
-      <c r="U10" t="n">
         <v>28</v>
       </c>
     </row>
@@ -2329,51 +2077,42 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7291666666666666</v>
+        <v>140</v>
       </c>
       <c r="G11" t="n">
         <v>0.7291666666666666</v>
       </c>
       <c r="H11" t="n">
-        <v>96</v>
+        <v>0.7291666666666666</v>
       </c>
       <c r="I11" t="n">
-        <v>130</v>
+        <v>0.6692307692307692</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6692307692307692</v>
+        <v>0.90625</v>
       </c>
       <c r="K11" t="n">
-        <v>0.90625</v>
+        <v>0.7699115044247788</v>
       </c>
       <c r="L11" t="n">
-        <v>0.7699115044247788</v>
+        <v>0.8548387096774194</v>
       </c>
       <c r="M11" t="n">
-        <v>96</v>
+        <v>0.5520833333333334</v>
       </c>
       <c r="N11" t="n">
-        <v>62</v>
+        <v>0.6708860759493671</v>
       </c>
       <c r="O11" t="n">
-        <v>0.8548387096774194</v>
+        <v>87</v>
       </c>
       <c r="P11" t="n">
-        <v>0.5520833333333334</v>
+        <v>9</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.6708860759493671</v>
+        <v>43</v>
       </c>
       <c r="R11" t="n">
-        <v>87</v>
-      </c>
-      <c r="S11" t="n">
-        <v>9</v>
-      </c>
-      <c r="T11" t="n">
-        <v>43</v>
-      </c>
-      <c r="U11" t="n">
         <v>53</v>
       </c>
     </row>
@@ -2396,51 +2135,42 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7395833333333334</v>
+        <v>142</v>
       </c>
       <c r="G12" t="n">
         <v>0.7395833333333334</v>
       </c>
       <c r="H12" t="n">
-        <v>96</v>
+        <v>0.7395833333333334</v>
       </c>
       <c r="I12" t="n">
-        <v>128</v>
+        <v>0.6796875</v>
       </c>
       <c r="J12" t="n">
-        <v>0.6796875</v>
+        <v>0.90625</v>
       </c>
       <c r="K12" t="n">
-        <v>0.90625</v>
+        <v>0.7767857142857143</v>
       </c>
       <c r="L12" t="n">
-        <v>0.7767857142857143</v>
+        <v>0.859375</v>
       </c>
       <c r="M12" t="n">
-        <v>96</v>
+        <v>0.5729166666666666</v>
       </c>
       <c r="N12" t="n">
-        <v>64</v>
+        <v>0.6875</v>
       </c>
       <c r="O12" t="n">
-        <v>0.859375</v>
+        <v>87</v>
       </c>
       <c r="P12" t="n">
-        <v>0.5729166666666666</v>
+        <v>9</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.6875</v>
+        <v>41</v>
       </c>
       <c r="R12" t="n">
-        <v>87</v>
-      </c>
-      <c r="S12" t="n">
-        <v>9</v>
-      </c>
-      <c r="T12" t="n">
-        <v>41</v>
-      </c>
-      <c r="U12" t="n">
         <v>55</v>
       </c>
     </row>
@@ -2463,51 +2193,42 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7395833333333334</v>
+        <v>142</v>
       </c>
       <c r="G13" t="n">
         <v>0.7395833333333334</v>
       </c>
       <c r="H13" t="n">
-        <v>96</v>
+        <v>0.7395833333333334</v>
       </c>
       <c r="I13" t="n">
-        <v>116</v>
+        <v>0.6982758620689655</v>
       </c>
       <c r="J13" t="n">
-        <v>0.6982758620689655</v>
+        <v>0.84375</v>
       </c>
       <c r="K13" t="n">
-        <v>0.84375</v>
+        <v>0.7641509433962264</v>
       </c>
       <c r="L13" t="n">
-        <v>0.7641509433962264</v>
+        <v>0.8026315789473685</v>
       </c>
       <c r="M13" t="n">
-        <v>96</v>
+        <v>0.6354166666666666</v>
       </c>
       <c r="N13" t="n">
-        <v>76</v>
+        <v>0.7093023255813953</v>
       </c>
       <c r="O13" t="n">
-        <v>0.8026315789473685</v>
+        <v>81</v>
       </c>
       <c r="P13" t="n">
-        <v>0.6354166666666666</v>
+        <v>15</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.7093023255813953</v>
+        <v>35</v>
       </c>
       <c r="R13" t="n">
-        <v>81</v>
-      </c>
-      <c r="S13" t="n">
-        <v>15</v>
-      </c>
-      <c r="T13" t="n">
-        <v>35</v>
-      </c>
-      <c r="U13" t="n">
         <v>61</v>
       </c>
     </row>
@@ -2530,51 +2251,42 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>0.78125</v>
+        <v>150</v>
       </c>
       <c r="G14" t="n">
         <v>0.78125</v>
       </c>
       <c r="H14" t="n">
-        <v>109</v>
+        <v>0.78125</v>
       </c>
       <c r="I14" t="n">
-        <v>137</v>
+        <v>0.7445255474452555</v>
       </c>
       <c r="J14" t="n">
-        <v>0.7445255474452555</v>
+        <v>0.9357798165137615</v>
       </c>
       <c r="K14" t="n">
-        <v>0.9357798165137615</v>
+        <v>0.8292682926829269</v>
       </c>
       <c r="L14" t="n">
-        <v>0.8292682926829269</v>
+        <v>0.8727272727272727</v>
       </c>
       <c r="M14" t="n">
-        <v>83</v>
+        <v>0.5783132530120482</v>
       </c>
       <c r="N14" t="n">
-        <v>55</v>
+        <v>0.6956521739130435</v>
       </c>
       <c r="O14" t="n">
-        <v>0.8727272727272727</v>
+        <v>102</v>
       </c>
       <c r="P14" t="n">
-        <v>0.5783132530120482</v>
+        <v>7</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.6956521739130435</v>
+        <v>35</v>
       </c>
       <c r="R14" t="n">
-        <v>102</v>
-      </c>
-      <c r="S14" t="n">
-        <v>7</v>
-      </c>
-      <c r="T14" t="n">
-        <v>35</v>
-      </c>
-      <c r="U14" t="n">
         <v>48</v>
       </c>
     </row>
@@ -2597,51 +2309,42 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6770833333333334</v>
+        <v>130</v>
       </c>
       <c r="G15" t="n">
         <v>0.6770833333333334</v>
       </c>
       <c r="H15" t="n">
-        <v>94</v>
+        <v>0.6770833333333334</v>
       </c>
       <c r="I15" t="n">
-        <v>146</v>
+        <v>0.6095890410958904</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6095890410958904</v>
+        <v>0.9468085106382979</v>
       </c>
       <c r="K15" t="n">
-        <v>0.9468085106382979</v>
+        <v>0.7416666666666667</v>
       </c>
       <c r="L15" t="n">
-        <v>0.7416666666666667</v>
+        <v>0.8913043478260869</v>
       </c>
       <c r="M15" t="n">
-        <v>98</v>
+        <v>0.4183673469387755</v>
       </c>
       <c r="N15" t="n">
-        <v>46</v>
+        <v>0.5694444444444445</v>
       </c>
       <c r="O15" t="n">
-        <v>0.8913043478260869</v>
+        <v>89</v>
       </c>
       <c r="P15" t="n">
-        <v>0.4183673469387755</v>
+        <v>5</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.5694444444444445</v>
+        <v>57</v>
       </c>
       <c r="R15" t="n">
-        <v>89</v>
-      </c>
-      <c r="S15" t="n">
-        <v>5</v>
-      </c>
-      <c r="T15" t="n">
-        <v>57</v>
-      </c>
-      <c r="U15" t="n">
         <v>41</v>
       </c>
     </row>
@@ -2664,51 +2367,42 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6510416666666666</v>
+        <v>125</v>
       </c>
       <c r="G16" t="n">
         <v>0.6510416666666666</v>
       </c>
       <c r="H16" t="n">
-        <v>90</v>
+        <v>0.6510416666666666</v>
       </c>
       <c r="I16" t="n">
-        <v>147</v>
+        <v>0.5782312925170068</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5782312925170068</v>
+        <v>0.9444444444444444</v>
       </c>
       <c r="K16" t="n">
-        <v>0.9444444444444444</v>
+        <v>0.7172995780590717</v>
       </c>
       <c r="L16" t="n">
-        <v>0.7172995780590717</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="M16" t="n">
-        <v>102</v>
+        <v>0.392156862745098</v>
       </c>
       <c r="N16" t="n">
-        <v>45</v>
+        <v>0.5442176870748299</v>
       </c>
       <c r="O16" t="n">
-        <v>0.8888888888888888</v>
+        <v>85</v>
       </c>
       <c r="P16" t="n">
-        <v>0.392156862745098</v>
+        <v>5</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.5442176870748299</v>
+        <v>62</v>
       </c>
       <c r="R16" t="n">
-        <v>85</v>
-      </c>
-      <c r="S16" t="n">
-        <v>5</v>
-      </c>
-      <c r="T16" t="n">
-        <v>62</v>
-      </c>
-      <c r="U16" t="n">
         <v>40</v>
       </c>
     </row>
@@ -2731,51 +2425,42 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6979166666666666</v>
+        <v>134</v>
       </c>
       <c r="G17" t="n">
         <v>0.6979166666666666</v>
       </c>
       <c r="H17" t="n">
-        <v>81</v>
+        <v>0.6979166666666666</v>
       </c>
       <c r="I17" t="n">
-        <v>125</v>
+        <v>0.592</v>
       </c>
       <c r="J17" t="n">
-        <v>0.592</v>
+        <v>0.9135802469135802</v>
       </c>
       <c r="K17" t="n">
-        <v>0.9135802469135802</v>
+        <v>0.7184466019417476</v>
       </c>
       <c r="L17" t="n">
-        <v>0.7184466019417476</v>
+        <v>0.8955223880597015</v>
       </c>
       <c r="M17" t="n">
-        <v>111</v>
+        <v>0.5405405405405406</v>
       </c>
       <c r="N17" t="n">
-        <v>67</v>
+        <v>0.6741573033707865</v>
       </c>
       <c r="O17" t="n">
-        <v>0.8955223880597015</v>
+        <v>74</v>
       </c>
       <c r="P17" t="n">
-        <v>0.5405405405405406</v>
+        <v>7</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.6741573033707865</v>
+        <v>51</v>
       </c>
       <c r="R17" t="n">
-        <v>74</v>
-      </c>
-      <c r="S17" t="n">
-        <v>7</v>
-      </c>
-      <c r="T17" t="n">
-        <v>51</v>
-      </c>
-      <c r="U17" t="n">
         <v>60</v>
       </c>
     </row>
@@ -2798,51 +2483,42 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6770833333333334</v>
+        <v>130</v>
       </c>
       <c r="G18" t="n">
         <v>0.6770833333333334</v>
       </c>
       <c r="H18" t="n">
-        <v>105</v>
+        <v>0.6770833333333334</v>
       </c>
       <c r="I18" t="n">
-        <v>137</v>
+        <v>0.656934306569343</v>
       </c>
       <c r="J18" t="n">
-        <v>0.656934306569343</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="K18" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.7438016528925619</v>
       </c>
       <c r="L18" t="n">
-        <v>0.7438016528925619</v>
+        <v>0.7272727272727273</v>
       </c>
       <c r="M18" t="n">
-        <v>87</v>
+        <v>0.4597701149425287</v>
       </c>
       <c r="N18" t="n">
-        <v>55</v>
+        <v>0.5633802816901408</v>
       </c>
       <c r="O18" t="n">
-        <v>0.7272727272727273</v>
+        <v>90</v>
       </c>
       <c r="P18" t="n">
-        <v>0.4597701149425287</v>
+        <v>15</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.5633802816901408</v>
+        <v>47</v>
       </c>
       <c r="R18" t="n">
-        <v>90</v>
-      </c>
-      <c r="S18" t="n">
-        <v>15</v>
-      </c>
-      <c r="T18" t="n">
-        <v>47</v>
-      </c>
-      <c r="U18" t="n">
         <v>40</v>
       </c>
     </row>
@@ -2865,51 +2541,42 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8072916666666666</v>
+        <v>155</v>
       </c>
       <c r="G19" t="n">
         <v>0.8072916666666666</v>
       </c>
       <c r="H19" t="n">
-        <v>97</v>
+        <v>0.8072916666666666</v>
       </c>
       <c r="I19" t="n">
-        <v>120</v>
+        <v>0.75</v>
       </c>
       <c r="J19" t="n">
-        <v>0.75</v>
+        <v>0.9278350515463918</v>
       </c>
       <c r="K19" t="n">
-        <v>0.9278350515463918</v>
+        <v>0.8294930875576036</v>
       </c>
       <c r="L19" t="n">
-        <v>0.8294930875576036</v>
+        <v>0.9027777777777778</v>
       </c>
       <c r="M19" t="n">
-        <v>95</v>
+        <v>0.6842105263157895</v>
       </c>
       <c r="N19" t="n">
-        <v>72</v>
+        <v>0.7784431137724551</v>
       </c>
       <c r="O19" t="n">
-        <v>0.9027777777777778</v>
+        <v>90</v>
       </c>
       <c r="P19" t="n">
-        <v>0.6842105263157895</v>
+        <v>7</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.7784431137724551</v>
+        <v>30</v>
       </c>
       <c r="R19" t="n">
-        <v>90</v>
-      </c>
-      <c r="S19" t="n">
-        <v>7</v>
-      </c>
-      <c r="T19" t="n">
-        <v>30</v>
-      </c>
-      <c r="U19" t="n">
         <v>65</v>
       </c>
     </row>
@@ -2932,51 +2599,42 @@
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>0.78125</v>
+        <v>150</v>
       </c>
       <c r="G20" t="n">
         <v>0.78125</v>
       </c>
       <c r="H20" t="n">
-        <v>83</v>
+        <v>0.78125</v>
       </c>
       <c r="I20" t="n">
-        <v>111</v>
+        <v>0.6846846846846847</v>
       </c>
       <c r="J20" t="n">
-        <v>0.6846846846846847</v>
+        <v>0.9156626506024096</v>
       </c>
       <c r="K20" t="n">
-        <v>0.9156626506024096</v>
+        <v>0.7835051546391752</v>
       </c>
       <c r="L20" t="n">
-        <v>0.7835051546391752</v>
+        <v>0.9135802469135802</v>
       </c>
       <c r="M20" t="n">
-        <v>109</v>
+        <v>0.6788990825688074</v>
       </c>
       <c r="N20" t="n">
-        <v>81</v>
+        <v>0.7789473684210526</v>
       </c>
       <c r="O20" t="n">
-        <v>0.9135802469135802</v>
+        <v>76</v>
       </c>
       <c r="P20" t="n">
-        <v>0.6788990825688074</v>
+        <v>7</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.7789473684210526</v>
+        <v>35</v>
       </c>
       <c r="R20" t="n">
-        <v>76</v>
-      </c>
-      <c r="S20" t="n">
-        <v>7</v>
-      </c>
-      <c r="T20" t="n">
-        <v>35</v>
-      </c>
-      <c r="U20" t="n">
         <v>74</v>
       </c>
     </row>
@@ -2999,51 +2657,42 @@
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>0.796875</v>
+        <v>153</v>
       </c>
       <c r="G21" t="n">
         <v>0.796875</v>
       </c>
       <c r="H21" t="n">
-        <v>99</v>
+        <v>0.796875</v>
       </c>
       <c r="I21" t="n">
-        <v>120</v>
+        <v>0.75</v>
       </c>
       <c r="J21" t="n">
-        <v>0.75</v>
+        <v>0.9090909090909091</v>
       </c>
       <c r="K21" t="n">
-        <v>0.9090909090909091</v>
+        <v>0.821917808219178</v>
       </c>
       <c r="L21" t="n">
-        <v>0.821917808219178</v>
+        <v>0.875</v>
       </c>
       <c r="M21" t="n">
-        <v>93</v>
+        <v>0.6774193548387096</v>
       </c>
       <c r="N21" t="n">
-        <v>72</v>
+        <v>0.7636363636363636</v>
       </c>
       <c r="O21" t="n">
-        <v>0.875</v>
+        <v>90</v>
       </c>
       <c r="P21" t="n">
-        <v>0.6774193548387096</v>
+        <v>9</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.7636363636363636</v>
+        <v>30</v>
       </c>
       <c r="R21" t="n">
-        <v>90</v>
-      </c>
-      <c r="S21" t="n">
-        <v>9</v>
-      </c>
-      <c r="T21" t="n">
-        <v>30</v>
-      </c>
-      <c r="U21" t="n">
         <v>63</v>
       </c>
     </row>
@@ -3066,51 +2715,42 @@
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>0.703125</v>
+        <v>135</v>
       </c>
       <c r="G22" t="n">
         <v>0.703125</v>
       </c>
       <c r="H22" t="n">
-        <v>81</v>
+        <v>0.703125</v>
       </c>
       <c r="I22" t="n">
-        <v>124</v>
+        <v>0.5967741935483871</v>
       </c>
       <c r="J22" t="n">
-        <v>0.5967741935483871</v>
+        <v>0.9135802469135802</v>
       </c>
       <c r="K22" t="n">
-        <v>0.9135802469135802</v>
+        <v>0.7219512195121951</v>
       </c>
       <c r="L22" t="n">
-        <v>0.7219512195121951</v>
+        <v>0.8970588235294118</v>
       </c>
       <c r="M22" t="n">
-        <v>111</v>
+        <v>0.5495495495495496</v>
       </c>
       <c r="N22" t="n">
-        <v>68</v>
+        <v>0.6815642458100559</v>
       </c>
       <c r="O22" t="n">
-        <v>0.8970588235294118</v>
+        <v>74</v>
       </c>
       <c r="P22" t="n">
-        <v>0.5495495495495496</v>
+        <v>7</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.6815642458100559</v>
+        <v>50</v>
       </c>
       <c r="R22" t="n">
-        <v>74</v>
-      </c>
-      <c r="S22" t="n">
-        <v>7</v>
-      </c>
-      <c r="T22" t="n">
-        <v>50</v>
-      </c>
-      <c r="U22" t="n">
         <v>61</v>
       </c>
     </row>
@@ -3133,51 +2773,42 @@
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>0.71875</v>
+        <v>138</v>
       </c>
       <c r="G23" t="n">
         <v>0.71875</v>
       </c>
       <c r="H23" t="n">
-        <v>84</v>
+        <v>0.71875</v>
       </c>
       <c r="I23" t="n">
-        <v>114</v>
+        <v>0.631578947368421</v>
       </c>
       <c r="J23" t="n">
-        <v>0.631578947368421</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="K23" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.7272727272727273</v>
       </c>
       <c r="L23" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.8461538461538461</v>
       </c>
       <c r="M23" t="n">
-        <v>108</v>
+        <v>0.6111111111111112</v>
       </c>
       <c r="N23" t="n">
-        <v>78</v>
+        <v>0.7096774193548387</v>
       </c>
       <c r="O23" t="n">
-        <v>0.8461538461538461</v>
+        <v>72</v>
       </c>
       <c r="P23" t="n">
-        <v>0.6111111111111112</v>
+        <v>12</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.7096774193548387</v>
+        <v>42</v>
       </c>
       <c r="R23" t="n">
-        <v>72</v>
-      </c>
-      <c r="S23" t="n">
-        <v>12</v>
-      </c>
-      <c r="T23" t="n">
-        <v>42</v>
-      </c>
-      <c r="U23" t="n">
         <v>66</v>
       </c>
     </row>
@@ -3200,51 +2831,42 @@
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>0.7760416666666666</v>
+        <v>149</v>
       </c>
       <c r="G24" t="n">
         <v>0.7760416666666666</v>
       </c>
       <c r="H24" t="n">
-        <v>88</v>
+        <v>0.7760416666666666</v>
       </c>
       <c r="I24" t="n">
-        <v>111</v>
+        <v>0.7027027027027027</v>
       </c>
       <c r="J24" t="n">
-        <v>0.7027027027027027</v>
+        <v>0.8863636363636364</v>
       </c>
       <c r="K24" t="n">
-        <v>0.8863636363636364</v>
+        <v>0.7839195979899497</v>
       </c>
       <c r="L24" t="n">
-        <v>0.7839195979899497</v>
+        <v>0.8765432098765432</v>
       </c>
       <c r="M24" t="n">
-        <v>104</v>
+        <v>0.6826923076923077</v>
       </c>
       <c r="N24" t="n">
-        <v>81</v>
+        <v>0.7675675675675676</v>
       </c>
       <c r="O24" t="n">
-        <v>0.8765432098765432</v>
+        <v>78</v>
       </c>
       <c r="P24" t="n">
-        <v>0.6826923076923077</v>
+        <v>10</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.7675675675675676</v>
+        <v>33</v>
       </c>
       <c r="R24" t="n">
-        <v>78</v>
-      </c>
-      <c r="S24" t="n">
-        <v>10</v>
-      </c>
-      <c r="T24" t="n">
-        <v>33</v>
-      </c>
-      <c r="U24" t="n">
         <v>71</v>
       </c>
     </row>
@@ -3267,51 +2889,42 @@
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>0.7447916666666666</v>
+        <v>143</v>
       </c>
       <c r="G25" t="n">
         <v>0.7447916666666666</v>
       </c>
       <c r="H25" t="n">
-        <v>99</v>
+        <v>0.7447916666666666</v>
       </c>
       <c r="I25" t="n">
-        <v>138</v>
+        <v>0.6811594202898551</v>
       </c>
       <c r="J25" t="n">
-        <v>0.6811594202898551</v>
+        <v>0.9494949494949495</v>
       </c>
       <c r="K25" t="n">
-        <v>0.9494949494949495</v>
+        <v>0.7932489451476793</v>
       </c>
       <c r="L25" t="n">
-        <v>0.7932489451476793</v>
+        <v>0.9074074074074074</v>
       </c>
       <c r="M25" t="n">
-        <v>93</v>
+        <v>0.5268817204301075</v>
       </c>
       <c r="N25" t="n">
-        <v>54</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="O25" t="n">
-        <v>0.9074074074074074</v>
+        <v>94</v>
       </c>
       <c r="P25" t="n">
-        <v>0.5268817204301075</v>
+        <v>5</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.6666666666666666</v>
+        <v>44</v>
       </c>
       <c r="R25" t="n">
-        <v>94</v>
-      </c>
-      <c r="S25" t="n">
-        <v>5</v>
-      </c>
-      <c r="T25" t="n">
-        <v>44</v>
-      </c>
-      <c r="U25" t="n">
         <v>49</v>
       </c>
     </row>
@@ -3334,51 +2947,42 @@
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>0.7552083333333334</v>
+        <v>145</v>
       </c>
       <c r="G26" t="n">
         <v>0.7552083333333334</v>
       </c>
       <c r="H26" t="n">
-        <v>87</v>
+        <v>0.7552083333333334</v>
       </c>
       <c r="I26" t="n">
-        <v>126</v>
+        <v>0.6587301587301587</v>
       </c>
       <c r="J26" t="n">
-        <v>0.6587301587301587</v>
+        <v>0.9540229885057471</v>
       </c>
       <c r="K26" t="n">
-        <v>0.9540229885057471</v>
+        <v>0.7793427230046948</v>
       </c>
       <c r="L26" t="n">
-        <v>0.7793427230046948</v>
+        <v>0.9393939393939394</v>
       </c>
       <c r="M26" t="n">
-        <v>105</v>
+        <v>0.5904761904761905</v>
       </c>
       <c r="N26" t="n">
-        <v>66</v>
+        <v>0.7251461988304092</v>
       </c>
       <c r="O26" t="n">
-        <v>0.9393939393939394</v>
+        <v>83</v>
       </c>
       <c r="P26" t="n">
-        <v>0.5904761904761905</v>
+        <v>4</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.7251461988304092</v>
+        <v>43</v>
       </c>
       <c r="R26" t="n">
-        <v>83</v>
-      </c>
-      <c r="S26" t="n">
-        <v>4</v>
-      </c>
-      <c r="T26" t="n">
-        <v>43</v>
-      </c>
-      <c r="U26" t="n">
         <v>62</v>
       </c>
     </row>
@@ -3401,51 +3005,42 @@
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>0.7291666666666666</v>
+        <v>140</v>
       </c>
       <c r="G27" t="n">
         <v>0.7291666666666666</v>
       </c>
       <c r="H27" t="n">
-        <v>101</v>
+        <v>0.7291666666666666</v>
       </c>
       <c r="I27" t="n">
-        <v>137</v>
+        <v>0.6788321167883211</v>
       </c>
       <c r="J27" t="n">
-        <v>0.6788321167883211</v>
+        <v>0.9207920792079208</v>
       </c>
       <c r="K27" t="n">
-        <v>0.9207920792079208</v>
+        <v>0.7815126050420168</v>
       </c>
       <c r="L27" t="n">
-        <v>0.7815126050420168</v>
+        <v>0.8545454545454545</v>
       </c>
       <c r="M27" t="n">
-        <v>91</v>
+        <v>0.5164835164835165</v>
       </c>
       <c r="N27" t="n">
-        <v>55</v>
+        <v>0.6438356164383563</v>
       </c>
       <c r="O27" t="n">
-        <v>0.8545454545454545</v>
+        <v>93</v>
       </c>
       <c r="P27" t="n">
-        <v>0.5164835164835165</v>
+        <v>8</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.6438356164383563</v>
+        <v>44</v>
       </c>
       <c r="R27" t="n">
-        <v>93</v>
-      </c>
-      <c r="S27" t="n">
-        <v>8</v>
-      </c>
-      <c r="T27" t="n">
-        <v>44</v>
-      </c>
-      <c r="U27" t="n">
         <v>47</v>
       </c>
     </row>
@@ -3468,51 +3063,42 @@
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>0.765625</v>
+        <v>147</v>
       </c>
       <c r="G28" t="n">
         <v>0.765625</v>
       </c>
       <c r="H28" t="n">
-        <v>95</v>
+        <v>0.765625</v>
       </c>
       <c r="I28" t="n">
-        <v>122</v>
+        <v>0.7049180327868853</v>
       </c>
       <c r="J28" t="n">
-        <v>0.7049180327868853</v>
+        <v>0.9052631578947369</v>
       </c>
       <c r="K28" t="n">
-        <v>0.9052631578947369</v>
+        <v>0.7926267281105991</v>
       </c>
       <c r="L28" t="n">
-        <v>0.7926267281105991</v>
+        <v>0.8714285714285714</v>
       </c>
       <c r="M28" t="n">
-        <v>97</v>
+        <v>0.6288659793814433</v>
       </c>
       <c r="N28" t="n">
-        <v>70</v>
+        <v>0.7305389221556887</v>
       </c>
       <c r="O28" t="n">
-        <v>0.8714285714285714</v>
+        <v>86</v>
       </c>
       <c r="P28" t="n">
-        <v>0.6288659793814433</v>
+        <v>9</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.7305389221556887</v>
+        <v>36</v>
       </c>
       <c r="R28" t="n">
-        <v>86</v>
-      </c>
-      <c r="S28" t="n">
-        <v>9</v>
-      </c>
-      <c r="T28" t="n">
-        <v>36</v>
-      </c>
-      <c r="U28" t="n">
         <v>61</v>
       </c>
     </row>
@@ -3535,51 +3121,42 @@
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>0.6666666666666666</v>
+        <v>128</v>
       </c>
       <c r="G29" t="n">
         <v>0.6666666666666666</v>
       </c>
       <c r="H29" t="n">
-        <v>90</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="I29" t="n">
-        <v>144</v>
+        <v>0.5902777777777778</v>
       </c>
       <c r="J29" t="n">
-        <v>0.5902777777777778</v>
+        <v>0.9444444444444444</v>
       </c>
       <c r="K29" t="n">
-        <v>0.9444444444444444</v>
+        <v>0.7264957264957265</v>
       </c>
       <c r="L29" t="n">
-        <v>0.7264957264957265</v>
+        <v>0.8958333333333334</v>
       </c>
       <c r="M29" t="n">
-        <v>102</v>
+        <v>0.4215686274509804</v>
       </c>
       <c r="N29" t="n">
-        <v>48</v>
+        <v>0.5733333333333334</v>
       </c>
       <c r="O29" t="n">
-        <v>0.8958333333333334</v>
+        <v>85</v>
       </c>
       <c r="P29" t="n">
-        <v>0.4215686274509804</v>
+        <v>5</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.5733333333333334</v>
+        <v>59</v>
       </c>
       <c r="R29" t="n">
-        <v>85</v>
-      </c>
-      <c r="S29" t="n">
-        <v>5</v>
-      </c>
-      <c r="T29" t="n">
-        <v>59</v>
-      </c>
-      <c r="U29" t="n">
         <v>43</v>
       </c>
     </row>
@@ -3602,51 +3179,42 @@
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>0.6927083333333334</v>
+        <v>133</v>
       </c>
       <c r="G30" t="n">
         <v>0.6927083333333334</v>
       </c>
       <c r="H30" t="n">
-        <v>99</v>
+        <v>0.6927083333333334</v>
       </c>
       <c r="I30" t="n">
-        <v>142</v>
+        <v>0.6408450704225352</v>
       </c>
       <c r="J30" t="n">
-        <v>0.6408450704225352</v>
+        <v>0.9191919191919192</v>
       </c>
       <c r="K30" t="n">
-        <v>0.9191919191919192</v>
+        <v>0.7551867219917012</v>
       </c>
       <c r="L30" t="n">
-        <v>0.7551867219917012</v>
+        <v>0.84</v>
       </c>
       <c r="M30" t="n">
-        <v>93</v>
+        <v>0.4516129032258064</v>
       </c>
       <c r="N30" t="n">
-        <v>50</v>
+        <v>0.5874125874125874</v>
       </c>
       <c r="O30" t="n">
-        <v>0.84</v>
+        <v>91</v>
       </c>
       <c r="P30" t="n">
-        <v>0.4516129032258064</v>
+        <v>8</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.5874125874125874</v>
+        <v>51</v>
       </c>
       <c r="R30" t="n">
-        <v>91</v>
-      </c>
-      <c r="S30" t="n">
-        <v>8</v>
-      </c>
-      <c r="T30" t="n">
-        <v>51</v>
-      </c>
-      <c r="U30" t="n">
         <v>42</v>
       </c>
     </row>
@@ -3669,51 +3237,42 @@
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>0.6927083333333334</v>
+        <v>133</v>
       </c>
       <c r="G31" t="n">
         <v>0.6927083333333334</v>
       </c>
       <c r="H31" t="n">
-        <v>92</v>
+        <v>0.6927083333333334</v>
       </c>
       <c r="I31" t="n">
-        <v>127</v>
+        <v>0.6299212598425197</v>
       </c>
       <c r="J31" t="n">
-        <v>0.6299212598425197</v>
+        <v>0.8695652173913043</v>
       </c>
       <c r="K31" t="n">
-        <v>0.8695652173913043</v>
+        <v>0.7305936073059359</v>
       </c>
       <c r="L31" t="n">
-        <v>0.7305936073059359</v>
+        <v>0.8153846153846154</v>
       </c>
       <c r="M31" t="n">
-        <v>100</v>
+        <v>0.53</v>
       </c>
       <c r="N31" t="n">
-        <v>65</v>
+        <v>0.6424242424242425</v>
       </c>
       <c r="O31" t="n">
-        <v>0.8153846153846154</v>
+        <v>80</v>
       </c>
       <c r="P31" t="n">
-        <v>0.53</v>
+        <v>12</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.6424242424242425</v>
+        <v>47</v>
       </c>
       <c r="R31" t="n">
-        <v>80</v>
-      </c>
-      <c r="S31" t="n">
-        <v>12</v>
-      </c>
-      <c r="T31" t="n">
-        <v>47</v>
-      </c>
-      <c r="U31" t="n">
         <v>53</v>
       </c>
     </row>
@@ -3736,51 +3295,42 @@
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>0.7239583333333334</v>
+        <v>139</v>
       </c>
       <c r="G32" t="n">
         <v>0.7239583333333334</v>
       </c>
       <c r="H32" t="n">
-        <v>89</v>
+        <v>0.7239583333333334</v>
       </c>
       <c r="I32" t="n">
-        <v>120</v>
+        <v>0.65</v>
       </c>
       <c r="J32" t="n">
-        <v>0.65</v>
+        <v>0.8764044943820225</v>
       </c>
       <c r="K32" t="n">
-        <v>0.8764044943820225</v>
+        <v>0.7464114832535885</v>
       </c>
       <c r="L32" t="n">
-        <v>0.7464114832535885</v>
+        <v>0.8472222222222222</v>
       </c>
       <c r="M32" t="n">
-        <v>103</v>
+        <v>0.5922330097087378</v>
       </c>
       <c r="N32" t="n">
-        <v>72</v>
+        <v>0.6971428571428572</v>
       </c>
       <c r="O32" t="n">
-        <v>0.8472222222222222</v>
+        <v>78</v>
       </c>
       <c r="P32" t="n">
-        <v>0.5922330097087378</v>
+        <v>11</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.6971428571428572</v>
+        <v>42</v>
       </c>
       <c r="R32" t="n">
-        <v>78</v>
-      </c>
-      <c r="S32" t="n">
-        <v>11</v>
-      </c>
-      <c r="T32" t="n">
-        <v>42</v>
-      </c>
-      <c r="U32" t="n">
         <v>61</v>
       </c>
     </row>
@@ -3803,51 +3353,42 @@
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>0.8020833333333334</v>
+        <v>154</v>
       </c>
       <c r="G33" t="n">
         <v>0.8020833333333334</v>
       </c>
       <c r="H33" t="n">
-        <v>94</v>
+        <v>0.8020833333333334</v>
       </c>
       <c r="I33" t="n">
-        <v>130</v>
+        <v>0.7153846153846154</v>
       </c>
       <c r="J33" t="n">
-        <v>0.7153846153846154</v>
+        <v>0.9893617021276596</v>
       </c>
       <c r="K33" t="n">
-        <v>0.9893617021276596</v>
+        <v>0.8303571428571428</v>
       </c>
       <c r="L33" t="n">
-        <v>0.8303571428571428</v>
+        <v>0.9838709677419355</v>
       </c>
       <c r="M33" t="n">
-        <v>98</v>
+        <v>0.6224489795918368</v>
       </c>
       <c r="N33" t="n">
-        <v>62</v>
+        <v>0.7625</v>
       </c>
       <c r="O33" t="n">
-        <v>0.9838709677419355</v>
+        <v>93</v>
       </c>
       <c r="P33" t="n">
-        <v>0.6224489795918368</v>
+        <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.7625</v>
+        <v>37</v>
       </c>
       <c r="R33" t="n">
-        <v>93</v>
-      </c>
-      <c r="S33" t="n">
-        <v>1</v>
-      </c>
-      <c r="T33" t="n">
-        <v>37</v>
-      </c>
-      <c r="U33" t="n">
         <v>61</v>
       </c>
     </row>
@@ -3870,51 +3411,42 @@
         <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>0.6822916666666666</v>
+        <v>131</v>
       </c>
       <c r="G34" t="n">
         <v>0.6822916666666666</v>
       </c>
       <c r="H34" t="n">
-        <v>93</v>
+        <v>0.6822916666666666</v>
       </c>
       <c r="I34" t="n">
-        <v>140</v>
+        <v>0.6142857142857143</v>
       </c>
       <c r="J34" t="n">
-        <v>0.6142857142857143</v>
+        <v>0.9247311827956989</v>
       </c>
       <c r="K34" t="n">
-        <v>0.9247311827956989</v>
+        <v>0.7381974248927038</v>
       </c>
       <c r="L34" t="n">
-        <v>0.7381974248927038</v>
+        <v>0.8653846153846154</v>
       </c>
       <c r="M34" t="n">
-        <v>99</v>
+        <v>0.4545454545454545</v>
       </c>
       <c r="N34" t="n">
-        <v>52</v>
+        <v>0.5960264900662251</v>
       </c>
       <c r="O34" t="n">
-        <v>0.8653846153846154</v>
+        <v>86</v>
       </c>
       <c r="P34" t="n">
-        <v>0.4545454545454545</v>
+        <v>7</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.5960264900662251</v>
+        <v>54</v>
       </c>
       <c r="R34" t="n">
-        <v>86</v>
-      </c>
-      <c r="S34" t="n">
-        <v>7</v>
-      </c>
-      <c r="T34" t="n">
-        <v>54</v>
-      </c>
-      <c r="U34" t="n">
         <v>45</v>
       </c>
     </row>
@@ -3937,51 +3469,42 @@
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>0.703125</v>
+        <v>135</v>
       </c>
       <c r="G35" t="n">
         <v>0.703125</v>
       </c>
       <c r="H35" t="n">
-        <v>92</v>
+        <v>0.703125</v>
       </c>
       <c r="I35" t="n">
-        <v>143</v>
+        <v>0.6223776223776224</v>
       </c>
       <c r="J35" t="n">
-        <v>0.6223776223776224</v>
+        <v>0.9673913043478261</v>
       </c>
       <c r="K35" t="n">
-        <v>0.9673913043478261</v>
+        <v>0.7574468085106383</v>
       </c>
       <c r="L35" t="n">
-        <v>0.7574468085106383</v>
+        <v>0.9387755102040817</v>
       </c>
       <c r="M35" t="n">
-        <v>100</v>
+        <v>0.46</v>
       </c>
       <c r="N35" t="n">
-        <v>49</v>
+        <v>0.6174496644295302</v>
       </c>
       <c r="O35" t="n">
-        <v>0.9387755102040817</v>
+        <v>89</v>
       </c>
       <c r="P35" t="n">
-        <v>0.46</v>
+        <v>3</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.6174496644295302</v>
+        <v>54</v>
       </c>
       <c r="R35" t="n">
-        <v>89</v>
-      </c>
-      <c r="S35" t="n">
-        <v>3</v>
-      </c>
-      <c r="T35" t="n">
-        <v>54</v>
-      </c>
-      <c r="U35" t="n">
         <v>46</v>
       </c>
     </row>
@@ -4004,51 +3527,42 @@
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>0.6614583333333334</v>
+        <v>127</v>
       </c>
       <c r="G36" t="n">
         <v>0.6614583333333334</v>
       </c>
       <c r="H36" t="n">
-        <v>84</v>
+        <v>0.6614583333333334</v>
       </c>
       <c r="I36" t="n">
-        <v>137</v>
+        <v>0.5693430656934306</v>
       </c>
       <c r="J36" t="n">
-        <v>0.5693430656934306</v>
+        <v>0.9285714285714286</v>
       </c>
       <c r="K36" t="n">
-        <v>0.9285714285714286</v>
+        <v>0.7058823529411765</v>
       </c>
       <c r="L36" t="n">
-        <v>0.7058823529411765</v>
+        <v>0.8909090909090909</v>
       </c>
       <c r="M36" t="n">
-        <v>108</v>
+        <v>0.4537037037037037</v>
       </c>
       <c r="N36" t="n">
-        <v>55</v>
+        <v>0.6012269938650306</v>
       </c>
       <c r="O36" t="n">
-        <v>0.8909090909090909</v>
+        <v>78</v>
       </c>
       <c r="P36" t="n">
-        <v>0.4537037037037037</v>
+        <v>6</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.6012269938650306</v>
+        <v>59</v>
       </c>
       <c r="R36" t="n">
-        <v>78</v>
-      </c>
-      <c r="S36" t="n">
-        <v>6</v>
-      </c>
-      <c r="T36" t="n">
-        <v>59</v>
-      </c>
-      <c r="U36" t="n">
         <v>49</v>
       </c>
     </row>
@@ -4071,51 +3585,42 @@
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>0.7239583333333334</v>
+        <v>139</v>
       </c>
       <c r="G37" t="n">
         <v>0.7239583333333334</v>
       </c>
       <c r="H37" t="n">
-        <v>100</v>
+        <v>0.7239583333333334</v>
       </c>
       <c r="I37" t="n">
-        <v>133</v>
+        <v>0.6766917293233082</v>
       </c>
       <c r="J37" t="n">
-        <v>0.6766917293233082</v>
+        <v>0.9</v>
       </c>
       <c r="K37" t="n">
-        <v>0.9</v>
+        <v>0.7725321888412018</v>
       </c>
       <c r="L37" t="n">
-        <v>0.7725321888412018</v>
+        <v>0.8305084745762712</v>
       </c>
       <c r="M37" t="n">
-        <v>92</v>
+        <v>0.5326086956521739</v>
       </c>
       <c r="N37" t="n">
-        <v>59</v>
+        <v>0.6490066225165564</v>
       </c>
       <c r="O37" t="n">
-        <v>0.8305084745762712</v>
+        <v>90</v>
       </c>
       <c r="P37" t="n">
-        <v>0.5326086956521739</v>
+        <v>10</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.6490066225165564</v>
+        <v>43</v>
       </c>
       <c r="R37" t="n">
-        <v>90</v>
-      </c>
-      <c r="S37" t="n">
-        <v>10</v>
-      </c>
-      <c r="T37" t="n">
-        <v>43</v>
-      </c>
-      <c r="U37" t="n">
         <v>49</v>
       </c>
     </row>
@@ -4138,51 +3643,42 @@
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>0.71875</v>
+        <v>138</v>
       </c>
       <c r="G38" t="n">
         <v>0.71875</v>
       </c>
       <c r="H38" t="n">
-        <v>98</v>
+        <v>0.71875</v>
       </c>
       <c r="I38" t="n">
-        <v>126</v>
+        <v>0.6746031746031746</v>
       </c>
       <c r="J38" t="n">
-        <v>0.6746031746031746</v>
+        <v>0.8673469387755102</v>
       </c>
       <c r="K38" t="n">
-        <v>0.8673469387755102</v>
+        <v>0.7589285714285715</v>
       </c>
       <c r="L38" t="n">
-        <v>0.7589285714285715</v>
+        <v>0.803030303030303</v>
       </c>
       <c r="M38" t="n">
-        <v>94</v>
+        <v>0.5638297872340425</v>
       </c>
       <c r="N38" t="n">
-        <v>66</v>
+        <v>0.6625</v>
       </c>
       <c r="O38" t="n">
-        <v>0.803030303030303</v>
+        <v>85</v>
       </c>
       <c r="P38" t="n">
-        <v>0.5638297872340425</v>
+        <v>13</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.6625</v>
+        <v>41</v>
       </c>
       <c r="R38" t="n">
-        <v>85</v>
-      </c>
-      <c r="S38" t="n">
-        <v>13</v>
-      </c>
-      <c r="T38" t="n">
-        <v>41</v>
-      </c>
-      <c r="U38" t="n">
         <v>53</v>
       </c>
     </row>
@@ -4205,51 +3701,42 @@
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>0.7135416666666666</v>
+        <v>137</v>
       </c>
       <c r="G39" t="n">
         <v>0.7135416666666666</v>
       </c>
       <c r="H39" t="n">
-        <v>84</v>
+        <v>0.7135416666666666</v>
       </c>
       <c r="I39" t="n">
-        <v>123</v>
+        <v>0.6178861788617886</v>
       </c>
       <c r="J39" t="n">
-        <v>0.6178861788617886</v>
+        <v>0.9047619047619048</v>
       </c>
       <c r="K39" t="n">
-        <v>0.9047619047619048</v>
+        <v>0.7342995169082125</v>
       </c>
       <c r="L39" t="n">
-        <v>0.7342995169082125</v>
+        <v>0.8840579710144928</v>
       </c>
       <c r="M39" t="n">
-        <v>108</v>
+        <v>0.5648148148148148</v>
       </c>
       <c r="N39" t="n">
-        <v>69</v>
+        <v>0.6892655367231638</v>
       </c>
       <c r="O39" t="n">
-        <v>0.8840579710144928</v>
+        <v>76</v>
       </c>
       <c r="P39" t="n">
-        <v>0.5648148148148148</v>
+        <v>8</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.6892655367231638</v>
+        <v>47</v>
       </c>
       <c r="R39" t="n">
-        <v>76</v>
-      </c>
-      <c r="S39" t="n">
-        <v>8</v>
-      </c>
-      <c r="T39" t="n">
-        <v>47</v>
-      </c>
-      <c r="U39" t="n">
         <v>61</v>
       </c>
     </row>
@@ -4272,51 +3759,42 @@
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>0.7135416666666666</v>
+        <v>137</v>
       </c>
       <c r="G40" t="n">
         <v>0.7135416666666666</v>
       </c>
       <c r="H40" t="n">
-        <v>98</v>
+        <v>0.7135416666666666</v>
       </c>
       <c r="I40" t="n">
-        <v>133</v>
+        <v>0.6616541353383458</v>
       </c>
       <c r="J40" t="n">
-        <v>0.6616541353383458</v>
+        <v>0.8979591836734694</v>
       </c>
       <c r="K40" t="n">
-        <v>0.8979591836734694</v>
+        <v>0.7619047619047619</v>
       </c>
       <c r="L40" t="n">
-        <v>0.7619047619047619</v>
+        <v>0.8305084745762712</v>
       </c>
       <c r="M40" t="n">
-        <v>94</v>
+        <v>0.5212765957446809</v>
       </c>
       <c r="N40" t="n">
-        <v>59</v>
+        <v>0.6405228758169934</v>
       </c>
       <c r="O40" t="n">
-        <v>0.8305084745762712</v>
+        <v>88</v>
       </c>
       <c r="P40" t="n">
-        <v>0.5212765957446809</v>
+        <v>10</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.6405228758169934</v>
+        <v>45</v>
       </c>
       <c r="R40" t="n">
-        <v>88</v>
-      </c>
-      <c r="S40" t="n">
-        <v>10</v>
-      </c>
-      <c r="T40" t="n">
-        <v>45</v>
-      </c>
-      <c r="U40" t="n">
         <v>49</v>
       </c>
     </row>
@@ -4339,51 +3817,42 @@
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>0.796875</v>
+        <v>153</v>
       </c>
       <c r="G41" t="n">
         <v>0.796875</v>
       </c>
       <c r="H41" t="n">
-        <v>105</v>
+        <v>0.796875</v>
       </c>
       <c r="I41" t="n">
-        <v>132</v>
+        <v>0.75</v>
       </c>
       <c r="J41" t="n">
-        <v>0.75</v>
+        <v>0.9428571428571428</v>
       </c>
       <c r="K41" t="n">
-        <v>0.9428571428571428</v>
+        <v>0.8354430379746834</v>
       </c>
       <c r="L41" t="n">
-        <v>0.8354430379746834</v>
+        <v>0.9</v>
       </c>
       <c r="M41" t="n">
-        <v>87</v>
+        <v>0.6206896551724138</v>
       </c>
       <c r="N41" t="n">
-        <v>60</v>
+        <v>0.7346938775510204</v>
       </c>
       <c r="O41" t="n">
-        <v>0.9</v>
+        <v>99</v>
       </c>
       <c r="P41" t="n">
-        <v>0.6206896551724138</v>
+        <v>6</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.7346938775510204</v>
+        <v>33</v>
       </c>
       <c r="R41" t="n">
-        <v>99</v>
-      </c>
-      <c r="S41" t="n">
-        <v>6</v>
-      </c>
-      <c r="T41" t="n">
-        <v>33</v>
-      </c>
-      <c r="U41" t="n">
         <v>54</v>
       </c>
     </row>
@@ -4406,51 +3875,42 @@
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>0.6458333333333334</v>
+        <v>124</v>
       </c>
       <c r="G42" t="n">
         <v>0.6458333333333334</v>
       </c>
       <c r="H42" t="n">
-        <v>89</v>
+        <v>0.6458333333333334</v>
       </c>
       <c r="I42" t="n">
-        <v>131</v>
+        <v>0.5801526717557252</v>
       </c>
       <c r="J42" t="n">
-        <v>0.5801526717557252</v>
+        <v>0.8539325842696629</v>
       </c>
       <c r="K42" t="n">
-        <v>0.8539325842696629</v>
+        <v>0.6909090909090908</v>
       </c>
       <c r="L42" t="n">
-        <v>0.6909090909090908</v>
+        <v>0.7868852459016393</v>
       </c>
       <c r="M42" t="n">
-        <v>103</v>
+        <v>0.4660194174757282</v>
       </c>
       <c r="N42" t="n">
-        <v>61</v>
+        <v>0.5853658536585367</v>
       </c>
       <c r="O42" t="n">
-        <v>0.7868852459016393</v>
+        <v>76</v>
       </c>
       <c r="P42" t="n">
-        <v>0.4660194174757282</v>
+        <v>13</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.5853658536585367</v>
+        <v>55</v>
       </c>
       <c r="R42" t="n">
-        <v>76</v>
-      </c>
-      <c r="S42" t="n">
-        <v>13</v>
-      </c>
-      <c r="T42" t="n">
-        <v>55</v>
-      </c>
-      <c r="U42" t="n">
         <v>48</v>
       </c>
     </row>
@@ -4473,51 +3933,42 @@
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>0.7395833333333334</v>
+        <v>142</v>
       </c>
       <c r="G43" t="n">
         <v>0.7395833333333334</v>
       </c>
       <c r="H43" t="n">
-        <v>98</v>
+        <v>0.7395833333333334</v>
       </c>
       <c r="I43" t="n">
-        <v>114</v>
+        <v>0.7105263157894737</v>
       </c>
       <c r="J43" t="n">
-        <v>0.7105263157894737</v>
+        <v>0.826530612244898</v>
       </c>
       <c r="K43" t="n">
-        <v>0.826530612244898</v>
+        <v>0.7641509433962264</v>
       </c>
       <c r="L43" t="n">
-        <v>0.7641509433962264</v>
+        <v>0.782051282051282</v>
       </c>
       <c r="M43" t="n">
-        <v>94</v>
+        <v>0.648936170212766</v>
       </c>
       <c r="N43" t="n">
-        <v>78</v>
+        <v>0.7093023255813954</v>
       </c>
       <c r="O43" t="n">
-        <v>0.782051282051282</v>
+        <v>81</v>
       </c>
       <c r="P43" t="n">
-        <v>0.648936170212766</v>
+        <v>17</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.7093023255813954</v>
+        <v>33</v>
       </c>
       <c r="R43" t="n">
-        <v>81</v>
-      </c>
-      <c r="S43" t="n">
-        <v>17</v>
-      </c>
-      <c r="T43" t="n">
-        <v>33</v>
-      </c>
-      <c r="U43" t="n">
         <v>61</v>
       </c>
     </row>
@@ -4540,51 +3991,42 @@
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>0.734375</v>
+        <v>141</v>
       </c>
       <c r="G44" t="n">
         <v>0.734375</v>
       </c>
       <c r="H44" t="n">
-        <v>111</v>
+        <v>0.734375</v>
       </c>
       <c r="I44" t="n">
-        <v>156</v>
+        <v>0.6923076923076923</v>
       </c>
       <c r="J44" t="n">
-        <v>0.6923076923076923</v>
+        <v>0.972972972972973</v>
       </c>
       <c r="K44" t="n">
-        <v>0.972972972972973</v>
+        <v>0.8089887640449438</v>
       </c>
       <c r="L44" t="n">
-        <v>0.8089887640449438</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="M44" t="n">
-        <v>81</v>
+        <v>0.4074074074074074</v>
       </c>
       <c r="N44" t="n">
-        <v>36</v>
+        <v>0.5641025641025641</v>
       </c>
       <c r="O44" t="n">
-        <v>0.9166666666666666</v>
+        <v>108</v>
       </c>
       <c r="P44" t="n">
-        <v>0.4074074074074074</v>
+        <v>3</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.5641025641025641</v>
+        <v>48</v>
       </c>
       <c r="R44" t="n">
-        <v>108</v>
-      </c>
-      <c r="S44" t="n">
-        <v>3</v>
-      </c>
-      <c r="T44" t="n">
-        <v>48</v>
-      </c>
-      <c r="U44" t="n">
         <v>33</v>
       </c>
     </row>
@@ -4607,51 +4049,42 @@
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>0.7447916666666666</v>
+        <v>143</v>
       </c>
       <c r="G45" t="n">
         <v>0.7447916666666666</v>
       </c>
       <c r="H45" t="n">
-        <v>95</v>
+        <v>0.7447916666666666</v>
       </c>
       <c r="I45" t="n">
-        <v>136</v>
+        <v>0.6691176470588235</v>
       </c>
       <c r="J45" t="n">
-        <v>0.6691176470588235</v>
+        <v>0.9578947368421052</v>
       </c>
       <c r="K45" t="n">
-        <v>0.9578947368421052</v>
+        <v>0.7878787878787878</v>
       </c>
       <c r="L45" t="n">
-        <v>0.7878787878787878</v>
+        <v>0.9285714285714286</v>
       </c>
       <c r="M45" t="n">
-        <v>97</v>
+        <v>0.5360824742268041</v>
       </c>
       <c r="N45" t="n">
-        <v>56</v>
+        <v>0.6797385620915032</v>
       </c>
       <c r="O45" t="n">
-        <v>0.9285714285714286</v>
+        <v>91</v>
       </c>
       <c r="P45" t="n">
-        <v>0.5360824742268041</v>
+        <v>4</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.6797385620915032</v>
+        <v>45</v>
       </c>
       <c r="R45" t="n">
-        <v>91</v>
-      </c>
-      <c r="S45" t="n">
-        <v>4</v>
-      </c>
-      <c r="T45" t="n">
-        <v>45</v>
-      </c>
-      <c r="U45" t="n">
         <v>52</v>
       </c>
     </row>
@@ -4674,51 +4107,42 @@
         <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>0.7708333333333334</v>
+        <v>148</v>
       </c>
       <c r="G46" t="n">
         <v>0.7708333333333334</v>
       </c>
       <c r="H46" t="n">
-        <v>102</v>
+        <v>0.7708333333333334</v>
       </c>
       <c r="I46" t="n">
-        <v>138</v>
+        <v>0.7101449275362319</v>
       </c>
       <c r="J46" t="n">
-        <v>0.7101449275362319</v>
+        <v>0.9607843137254902</v>
       </c>
       <c r="K46" t="n">
-        <v>0.9607843137254902</v>
+        <v>0.8166666666666667</v>
       </c>
       <c r="L46" t="n">
-        <v>0.8166666666666667</v>
+        <v>0.9259259259259259</v>
       </c>
       <c r="M46" t="n">
-        <v>90</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="N46" t="n">
-        <v>54</v>
+        <v>0.6944444444444444</v>
       </c>
       <c r="O46" t="n">
-        <v>0.9259259259259259</v>
+        <v>98</v>
       </c>
       <c r="P46" t="n">
-        <v>0.5555555555555556</v>
+        <v>4</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.6944444444444444</v>
+        <v>40</v>
       </c>
       <c r="R46" t="n">
-        <v>98</v>
-      </c>
-      <c r="S46" t="n">
-        <v>4</v>
-      </c>
-      <c r="T46" t="n">
-        <v>40</v>
-      </c>
-      <c r="U46" t="n">
         <v>50</v>
       </c>
     </row>
@@ -4741,51 +4165,42 @@
         <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>0.75</v>
+        <v>144</v>
       </c>
       <c r="G47" t="n">
         <v>0.75</v>
       </c>
       <c r="H47" t="n">
-        <v>99</v>
+        <v>0.75</v>
       </c>
       <c r="I47" t="n">
-        <v>127</v>
+        <v>0.7007874015748031</v>
       </c>
       <c r="J47" t="n">
-        <v>0.7007874015748031</v>
+        <v>0.898989898989899</v>
       </c>
       <c r="K47" t="n">
-        <v>0.898989898989899</v>
+        <v>0.7876106194690267</v>
       </c>
       <c r="L47" t="n">
-        <v>0.7876106194690267</v>
+        <v>0.8461538461538461</v>
       </c>
       <c r="M47" t="n">
-        <v>93</v>
+        <v>0.5913978494623656</v>
       </c>
       <c r="N47" t="n">
-        <v>65</v>
+        <v>0.6962025316455697</v>
       </c>
       <c r="O47" t="n">
-        <v>0.8461538461538461</v>
+        <v>89</v>
       </c>
       <c r="P47" t="n">
-        <v>0.5913978494623656</v>
+        <v>10</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.6962025316455697</v>
+        <v>38</v>
       </c>
       <c r="R47" t="n">
-        <v>89</v>
-      </c>
-      <c r="S47" t="n">
-        <v>10</v>
-      </c>
-      <c r="T47" t="n">
-        <v>38</v>
-      </c>
-      <c r="U47" t="n">
         <v>55</v>
       </c>
     </row>
@@ -4808,51 +4223,42 @@
         <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>0.7083333333333334</v>
+        <v>136</v>
       </c>
       <c r="G48" t="n">
         <v>0.7083333333333334</v>
       </c>
       <c r="H48" t="n">
-        <v>93</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="I48" t="n">
-        <v>135</v>
+        <v>0.6370370370370371</v>
       </c>
       <c r="J48" t="n">
-        <v>0.6370370370370371</v>
+        <v>0.9247311827956989</v>
       </c>
       <c r="K48" t="n">
-        <v>0.9247311827956989</v>
+        <v>0.7543859649122808</v>
       </c>
       <c r="L48" t="n">
-        <v>0.7543859649122808</v>
+        <v>0.8771929824561403</v>
       </c>
       <c r="M48" t="n">
-        <v>99</v>
+        <v>0.5050505050505051</v>
       </c>
       <c r="N48" t="n">
-        <v>57</v>
+        <v>0.641025641025641</v>
       </c>
       <c r="O48" t="n">
-        <v>0.8771929824561403</v>
+        <v>86</v>
       </c>
       <c r="P48" t="n">
-        <v>0.5050505050505051</v>
+        <v>7</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.641025641025641</v>
+        <v>49</v>
       </c>
       <c r="R48" t="n">
-        <v>86</v>
-      </c>
-      <c r="S48" t="n">
-        <v>7</v>
-      </c>
-      <c r="T48" t="n">
-        <v>49</v>
-      </c>
-      <c r="U48" t="n">
         <v>50</v>
       </c>
     </row>
@@ -4875,51 +4281,42 @@
         <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>0.734375</v>
+        <v>141</v>
       </c>
       <c r="G49" t="n">
         <v>0.734375</v>
       </c>
       <c r="H49" t="n">
-        <v>87</v>
+        <v>0.734375</v>
       </c>
       <c r="I49" t="n">
-        <v>124</v>
+        <v>0.6451612903225806</v>
       </c>
       <c r="J49" t="n">
-        <v>0.6451612903225806</v>
+        <v>0.9195402298850575</v>
       </c>
       <c r="K49" t="n">
-        <v>0.9195402298850575</v>
+        <v>0.7582938388625592</v>
       </c>
       <c r="L49" t="n">
-        <v>0.7582938388625592</v>
+        <v>0.8970588235294118</v>
       </c>
       <c r="M49" t="n">
-        <v>105</v>
+        <v>0.580952380952381</v>
       </c>
       <c r="N49" t="n">
-        <v>68</v>
+        <v>0.7052023121387283</v>
       </c>
       <c r="O49" t="n">
-        <v>0.8970588235294118</v>
+        <v>80</v>
       </c>
       <c r="P49" t="n">
-        <v>0.580952380952381</v>
+        <v>7</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.7052023121387283</v>
+        <v>44</v>
       </c>
       <c r="R49" t="n">
-        <v>80</v>
-      </c>
-      <c r="S49" t="n">
-        <v>7</v>
-      </c>
-      <c r="T49" t="n">
-        <v>44</v>
-      </c>
-      <c r="U49" t="n">
         <v>61</v>
       </c>
     </row>
@@ -4942,51 +4339,42 @@
         <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>0.734375</v>
+        <v>141</v>
       </c>
       <c r="G50" t="n">
         <v>0.734375</v>
       </c>
       <c r="H50" t="n">
-        <v>88</v>
+        <v>0.734375</v>
       </c>
       <c r="I50" t="n">
-        <v>125</v>
+        <v>0.648</v>
       </c>
       <c r="J50" t="n">
-        <v>0.648</v>
+        <v>0.9204545454545454</v>
       </c>
       <c r="K50" t="n">
-        <v>0.9204545454545454</v>
+        <v>0.7605633802816901</v>
       </c>
       <c r="L50" t="n">
-        <v>0.7605633802816901</v>
+        <v>0.8955223880597015</v>
       </c>
       <c r="M50" t="n">
-        <v>104</v>
+        <v>0.5769230769230769</v>
       </c>
       <c r="N50" t="n">
-        <v>67</v>
+        <v>0.7017543859649121</v>
       </c>
       <c r="O50" t="n">
-        <v>0.8955223880597015</v>
+        <v>81</v>
       </c>
       <c r="P50" t="n">
-        <v>0.5769230769230769</v>
+        <v>7</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.7017543859649121</v>
+        <v>44</v>
       </c>
       <c r="R50" t="n">
-        <v>81</v>
-      </c>
-      <c r="S50" t="n">
-        <v>7</v>
-      </c>
-      <c r="T50" t="n">
-        <v>44</v>
-      </c>
-      <c r="U50" t="n">
         <v>60</v>
       </c>
     </row>
@@ -5009,51 +4397,42 @@
         <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>0.8697916666666666</v>
+        <v>167</v>
       </c>
       <c r="G51" t="n">
         <v>0.8697916666666666</v>
       </c>
       <c r="H51" t="n">
-        <v>88</v>
+        <v>0.8697916666666666</v>
       </c>
       <c r="I51" t="n">
-        <v>97</v>
+        <v>0.8247422680412371</v>
       </c>
       <c r="J51" t="n">
-        <v>0.8247422680412371</v>
+        <v>0.9090909090909091</v>
       </c>
       <c r="K51" t="n">
-        <v>0.9090909090909091</v>
+        <v>0.8648648648648649</v>
       </c>
       <c r="L51" t="n">
-        <v>0.8648648648648649</v>
+        <v>0.9157894736842105</v>
       </c>
       <c r="M51" t="n">
-        <v>104</v>
+        <v>0.8365384615384616</v>
       </c>
       <c r="N51" t="n">
-        <v>95</v>
+        <v>0.8743718592964824</v>
       </c>
       <c r="O51" t="n">
-        <v>0.9157894736842105</v>
+        <v>80</v>
       </c>
       <c r="P51" t="n">
-        <v>0.8365384615384616</v>
+        <v>8</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.8743718592964824</v>
+        <v>17</v>
       </c>
       <c r="R51" t="n">
-        <v>80</v>
-      </c>
-      <c r="S51" t="n">
-        <v>8</v>
-      </c>
-      <c r="T51" t="n">
-        <v>17</v>
-      </c>
-      <c r="U51" t="n">
         <v>87</v>
       </c>
     </row>
@@ -5076,51 +4455,42 @@
         <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>0.7708333333333334</v>
+        <v>148</v>
       </c>
       <c r="G52" t="n">
         <v>0.7708333333333334</v>
       </c>
       <c r="H52" t="n">
-        <v>93</v>
+        <v>0.7708333333333334</v>
       </c>
       <c r="I52" t="n">
-        <v>121</v>
+        <v>0.7024793388429752</v>
       </c>
       <c r="J52" t="n">
-        <v>0.7024793388429752</v>
+        <v>0.9139784946236559</v>
       </c>
       <c r="K52" t="n">
-        <v>0.9139784946236559</v>
+        <v>0.7943925233644861</v>
       </c>
       <c r="L52" t="n">
-        <v>0.7943925233644861</v>
+        <v>0.8873239436619719</v>
       </c>
       <c r="M52" t="n">
-        <v>99</v>
+        <v>0.6363636363636364</v>
       </c>
       <c r="N52" t="n">
-        <v>71</v>
+        <v>0.7411764705882353</v>
       </c>
       <c r="O52" t="n">
-        <v>0.8873239436619719</v>
+        <v>85</v>
       </c>
       <c r="P52" t="n">
-        <v>0.6363636363636364</v>
+        <v>8</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.7411764705882353</v>
+        <v>36</v>
       </c>
       <c r="R52" t="n">
-        <v>85</v>
-      </c>
-      <c r="S52" t="n">
-        <v>8</v>
-      </c>
-      <c r="T52" t="n">
-        <v>36</v>
-      </c>
-      <c r="U52" t="n">
         <v>63</v>
       </c>
     </row>
@@ -5143,51 +4513,42 @@
         <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>0.6979166666666666</v>
+        <v>134</v>
       </c>
       <c r="G53" t="n">
         <v>0.6979166666666666</v>
       </c>
       <c r="H53" t="n">
-        <v>95</v>
+        <v>0.6979166666666666</v>
       </c>
       <c r="I53" t="n">
-        <v>143</v>
+        <v>0.6293706293706294</v>
       </c>
       <c r="J53" t="n">
-        <v>0.6293706293706294</v>
+        <v>0.9473684210526315</v>
       </c>
       <c r="K53" t="n">
-        <v>0.9473684210526315</v>
+        <v>0.7563025210084032</v>
       </c>
       <c r="L53" t="n">
-        <v>0.7563025210084032</v>
+        <v>0.8979591836734694</v>
       </c>
       <c r="M53" t="n">
-        <v>97</v>
+        <v>0.4536082474226804</v>
       </c>
       <c r="N53" t="n">
-        <v>49</v>
+        <v>0.6027397260273972</v>
       </c>
       <c r="O53" t="n">
-        <v>0.8979591836734694</v>
+        <v>90</v>
       </c>
       <c r="P53" t="n">
-        <v>0.4536082474226804</v>
+        <v>5</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.6027397260273972</v>
+        <v>53</v>
       </c>
       <c r="R53" t="n">
-        <v>90</v>
-      </c>
-      <c r="S53" t="n">
-        <v>5</v>
-      </c>
-      <c r="T53" t="n">
-        <v>53</v>
-      </c>
-      <c r="U53" t="n">
         <v>44</v>
       </c>
     </row>
@@ -5210,51 +4571,42 @@
         <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>0.765625</v>
+        <v>147</v>
       </c>
       <c r="G54" t="n">
         <v>0.765625</v>
       </c>
       <c r="H54" t="n">
-        <v>99</v>
+        <v>0.765625</v>
       </c>
       <c r="I54" t="n">
-        <v>134</v>
+        <v>0.7014925373134329</v>
       </c>
       <c r="J54" t="n">
-        <v>0.7014925373134329</v>
+        <v>0.9494949494949495</v>
       </c>
       <c r="K54" t="n">
-        <v>0.9494949494949495</v>
+        <v>0.8068669527896997</v>
       </c>
       <c r="L54" t="n">
-        <v>0.8068669527896997</v>
+        <v>0.9137931034482759</v>
       </c>
       <c r="M54" t="n">
-        <v>93</v>
+        <v>0.5698924731182796</v>
       </c>
       <c r="N54" t="n">
-        <v>58</v>
+        <v>0.7019867549668874</v>
       </c>
       <c r="O54" t="n">
-        <v>0.9137931034482759</v>
+        <v>94</v>
       </c>
       <c r="P54" t="n">
-        <v>0.5698924731182796</v>
+        <v>5</v>
       </c>
       <c r="Q54" t="n">
-        <v>0.7019867549668874</v>
+        <v>40</v>
       </c>
       <c r="R54" t="n">
-        <v>94</v>
-      </c>
-      <c r="S54" t="n">
-        <v>5</v>
-      </c>
-      <c r="T54" t="n">
-        <v>40</v>
-      </c>
-      <c r="U54" t="n">
         <v>53</v>
       </c>
     </row>
@@ -5277,51 +4629,42 @@
         <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>0.8177083333333334</v>
+        <v>157</v>
       </c>
       <c r="G55" t="n">
         <v>0.8177083333333334</v>
       </c>
       <c r="H55" t="n">
-        <v>90</v>
+        <v>0.8177083333333334</v>
       </c>
       <c r="I55" t="n">
-        <v>107</v>
+        <v>0.7570093457943925</v>
       </c>
       <c r="J55" t="n">
-        <v>0.7570093457943925</v>
+        <v>0.9</v>
       </c>
       <c r="K55" t="n">
-        <v>0.9</v>
+        <v>0.8223350253807106</v>
       </c>
       <c r="L55" t="n">
-        <v>0.8223350253807106</v>
+        <v>0.8941176470588236</v>
       </c>
       <c r="M55" t="n">
-        <v>102</v>
+        <v>0.7450980392156863</v>
       </c>
       <c r="N55" t="n">
-        <v>85</v>
+        <v>0.8128342245989305</v>
       </c>
       <c r="O55" t="n">
-        <v>0.8941176470588236</v>
+        <v>81</v>
       </c>
       <c r="P55" t="n">
-        <v>0.7450980392156863</v>
+        <v>9</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.8128342245989305</v>
+        <v>26</v>
       </c>
       <c r="R55" t="n">
-        <v>81</v>
-      </c>
-      <c r="S55" t="n">
-        <v>9</v>
-      </c>
-      <c r="T55" t="n">
-        <v>26</v>
-      </c>
-      <c r="U55" t="n">
         <v>76</v>
       </c>
     </row>
@@ -5344,51 +4687,42 @@
         <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>0.78125</v>
+        <v>150</v>
       </c>
       <c r="G56" t="n">
         <v>0.78125</v>
       </c>
       <c r="H56" t="n">
-        <v>94</v>
+        <v>0.78125</v>
       </c>
       <c r="I56" t="n">
-        <v>126</v>
+        <v>0.7063492063492064</v>
       </c>
       <c r="J56" t="n">
-        <v>0.7063492063492064</v>
+        <v>0.9468085106382979</v>
       </c>
       <c r="K56" t="n">
-        <v>0.9468085106382979</v>
+        <v>0.8090909090909091</v>
       </c>
       <c r="L56" t="n">
-        <v>0.8090909090909091</v>
+        <v>0.9242424242424242</v>
       </c>
       <c r="M56" t="n">
-        <v>98</v>
+        <v>0.6224489795918368</v>
       </c>
       <c r="N56" t="n">
-        <v>66</v>
+        <v>0.7439024390243902</v>
       </c>
       <c r="O56" t="n">
-        <v>0.9242424242424242</v>
+        <v>89</v>
       </c>
       <c r="P56" t="n">
-        <v>0.6224489795918368</v>
+        <v>5</v>
       </c>
       <c r="Q56" t="n">
-        <v>0.7439024390243902</v>
+        <v>37</v>
       </c>
       <c r="R56" t="n">
-        <v>89</v>
-      </c>
-      <c r="S56" t="n">
-        <v>5</v>
-      </c>
-      <c r="T56" t="n">
-        <v>37</v>
-      </c>
-      <c r="U56" t="n">
         <v>61</v>
       </c>
     </row>
@@ -5411,51 +4745,42 @@
         <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>0.78125</v>
+        <v>150</v>
       </c>
       <c r="G57" t="n">
         <v>0.78125</v>
       </c>
       <c r="H57" t="n">
-        <v>95</v>
+        <v>0.78125</v>
       </c>
       <c r="I57" t="n">
-        <v>123</v>
+        <v>0.7154471544715447</v>
       </c>
       <c r="J57" t="n">
-        <v>0.7154471544715447</v>
+        <v>0.9263157894736842</v>
       </c>
       <c r="K57" t="n">
-        <v>0.9263157894736842</v>
+        <v>0.8073394495412844</v>
       </c>
       <c r="L57" t="n">
-        <v>0.8073394495412844</v>
+        <v>0.8985507246376812</v>
       </c>
       <c r="M57" t="n">
-        <v>97</v>
+        <v>0.6391752577319587</v>
       </c>
       <c r="N57" t="n">
-        <v>69</v>
+        <v>0.7469879518072289</v>
       </c>
       <c r="O57" t="n">
-        <v>0.8985507246376812</v>
+        <v>88</v>
       </c>
       <c r="P57" t="n">
-        <v>0.6391752577319587</v>
+        <v>7</v>
       </c>
       <c r="Q57" t="n">
-        <v>0.7469879518072289</v>
+        <v>35</v>
       </c>
       <c r="R57" t="n">
-        <v>88</v>
-      </c>
-      <c r="S57" t="n">
-        <v>7</v>
-      </c>
-      <c r="T57" t="n">
-        <v>35</v>
-      </c>
-      <c r="U57" t="n">
         <v>62</v>
       </c>
     </row>
@@ -5478,51 +4803,42 @@
         <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>0.7708333333333334</v>
+        <v>148</v>
       </c>
       <c r="G58" t="n">
         <v>0.7708333333333334</v>
       </c>
       <c r="H58" t="n">
-        <v>91</v>
+        <v>0.7708333333333334</v>
       </c>
       <c r="I58" t="n">
-        <v>127</v>
+        <v>0.6850393700787402</v>
       </c>
       <c r="J58" t="n">
-        <v>0.6850393700787402</v>
+        <v>0.9560439560439561</v>
       </c>
       <c r="K58" t="n">
-        <v>0.9560439560439561</v>
+        <v>0.798165137614679</v>
       </c>
       <c r="L58" t="n">
-        <v>0.798165137614679</v>
+        <v>0.9384615384615385</v>
       </c>
       <c r="M58" t="n">
-        <v>101</v>
+        <v>0.6039603960396039</v>
       </c>
       <c r="N58" t="n">
-        <v>65</v>
+        <v>0.7349397590361446</v>
       </c>
       <c r="O58" t="n">
-        <v>0.9384615384615385</v>
+        <v>87</v>
       </c>
       <c r="P58" t="n">
-        <v>0.6039603960396039</v>
+        <v>4</v>
       </c>
       <c r="Q58" t="n">
-        <v>0.7349397590361446</v>
+        <v>40</v>
       </c>
       <c r="R58" t="n">
-        <v>87</v>
-      </c>
-      <c r="S58" t="n">
-        <v>4</v>
-      </c>
-      <c r="T58" t="n">
-        <v>40</v>
-      </c>
-      <c r="U58" t="n">
         <v>61</v>
       </c>
     </row>
@@ -5545,51 +4861,42 @@
         <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>0.703125</v>
+        <v>135</v>
       </c>
       <c r="G59" t="n">
         <v>0.703125</v>
       </c>
       <c r="H59" t="n">
-        <v>88</v>
+        <v>0.703125</v>
       </c>
       <c r="I59" t="n">
-        <v>137</v>
+        <v>0.6131386861313869</v>
       </c>
       <c r="J59" t="n">
-        <v>0.6131386861313869</v>
+        <v>0.9545454545454546</v>
       </c>
       <c r="K59" t="n">
-        <v>0.9545454545454546</v>
+        <v>0.7466666666666667</v>
       </c>
       <c r="L59" t="n">
-        <v>0.7466666666666667</v>
+        <v>0.9272727272727272</v>
       </c>
       <c r="M59" t="n">
-        <v>104</v>
+        <v>0.4903846153846154</v>
       </c>
       <c r="N59" t="n">
-        <v>55</v>
+        <v>0.6415094339622641</v>
       </c>
       <c r="O59" t="n">
-        <v>0.9272727272727272</v>
+        <v>84</v>
       </c>
       <c r="P59" t="n">
-        <v>0.4903846153846154</v>
+        <v>4</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.6415094339622641</v>
+        <v>53</v>
       </c>
       <c r="R59" t="n">
-        <v>84</v>
-      </c>
-      <c r="S59" t="n">
-        <v>4</v>
-      </c>
-      <c r="T59" t="n">
-        <v>53</v>
-      </c>
-      <c r="U59" t="n">
         <v>51</v>
       </c>
     </row>
@@ -5612,51 +4919,42 @@
         <v>0</v>
       </c>
       <c r="F60" t="n">
-        <v>0.7864583333333334</v>
+        <v>151</v>
       </c>
       <c r="G60" t="n">
         <v>0.7864583333333334</v>
       </c>
       <c r="H60" t="n">
-        <v>111</v>
+        <v>0.7864583333333334</v>
       </c>
       <c r="I60" t="n">
-        <v>136</v>
+        <v>0.7573529411764706</v>
       </c>
       <c r="J60" t="n">
-        <v>0.7573529411764706</v>
+        <v>0.9279279279279279</v>
       </c>
       <c r="K60" t="n">
-        <v>0.9279279279279279</v>
+        <v>0.834008097165992</v>
       </c>
       <c r="L60" t="n">
-        <v>0.834008097165992</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="M60" t="n">
-        <v>81</v>
+        <v>0.5925925925925926</v>
       </c>
       <c r="N60" t="n">
-        <v>56</v>
+        <v>0.7007299270072992</v>
       </c>
       <c r="O60" t="n">
-        <v>0.8571428571428571</v>
+        <v>103</v>
       </c>
       <c r="P60" t="n">
-        <v>0.5925925925925926</v>
+        <v>8</v>
       </c>
       <c r="Q60" t="n">
-        <v>0.7007299270072992</v>
+        <v>33</v>
       </c>
       <c r="R60" t="n">
-        <v>103</v>
-      </c>
-      <c r="S60" t="n">
-        <v>8</v>
-      </c>
-      <c r="T60" t="n">
-        <v>33</v>
-      </c>
-      <c r="U60" t="n">
         <v>48</v>
       </c>
     </row>
@@ -5679,51 +4977,42 @@
         <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>0.765625</v>
+        <v>147</v>
       </c>
       <c r="G61" t="n">
         <v>0.765625</v>
       </c>
       <c r="H61" t="n">
-        <v>98</v>
+        <v>0.765625</v>
       </c>
       <c r="I61" t="n">
-        <v>127</v>
+        <v>0.7086614173228346</v>
       </c>
       <c r="J61" t="n">
-        <v>0.7086614173228346</v>
+        <v>0.9183673469387755</v>
       </c>
       <c r="K61" t="n">
-        <v>0.9183673469387755</v>
+        <v>0.8</v>
       </c>
       <c r="L61" t="n">
-        <v>0.8</v>
+        <v>0.8769230769230769</v>
       </c>
       <c r="M61" t="n">
-        <v>94</v>
+        <v>0.6063829787234043</v>
       </c>
       <c r="N61" t="n">
-        <v>65</v>
+        <v>0.7169811320754718</v>
       </c>
       <c r="O61" t="n">
-        <v>0.8769230769230769</v>
+        <v>90</v>
       </c>
       <c r="P61" t="n">
-        <v>0.6063829787234043</v>
+        <v>8</v>
       </c>
       <c r="Q61" t="n">
-        <v>0.7169811320754718</v>
+        <v>37</v>
       </c>
       <c r="R61" t="n">
-        <v>90</v>
-      </c>
-      <c r="S61" t="n">
-        <v>8</v>
-      </c>
-      <c r="T61" t="n">
-        <v>37</v>
-      </c>
-      <c r="U61" t="n">
         <v>57</v>
       </c>
     </row>
@@ -5746,51 +5035,42 @@
         <v>0</v>
       </c>
       <c r="F62" t="n">
-        <v>0.75</v>
+        <v>144</v>
       </c>
       <c r="G62" t="n">
         <v>0.75</v>
       </c>
       <c r="H62" t="n">
-        <v>106</v>
+        <v>0.75</v>
       </c>
       <c r="I62" t="n">
-        <v>128</v>
+        <v>0.7265625</v>
       </c>
       <c r="J62" t="n">
-        <v>0.7265625</v>
+        <v>0.8773584905660378</v>
       </c>
       <c r="K62" t="n">
-        <v>0.8773584905660378</v>
+        <v>0.7948717948717949</v>
       </c>
       <c r="L62" t="n">
-        <v>0.7948717948717949</v>
+        <v>0.796875</v>
       </c>
       <c r="M62" t="n">
-        <v>86</v>
+        <v>0.5930232558139535</v>
       </c>
       <c r="N62" t="n">
-        <v>64</v>
+        <v>0.6799999999999999</v>
       </c>
       <c r="O62" t="n">
-        <v>0.796875</v>
+        <v>93</v>
       </c>
       <c r="P62" t="n">
-        <v>0.5930232558139535</v>
+        <v>13</v>
       </c>
       <c r="Q62" t="n">
-        <v>0.6799999999999999</v>
+        <v>35</v>
       </c>
       <c r="R62" t="n">
-        <v>93</v>
-      </c>
-      <c r="S62" t="n">
-        <v>13</v>
-      </c>
-      <c r="T62" t="n">
-        <v>35</v>
-      </c>
-      <c r="U62" t="n">
         <v>51</v>
       </c>
     </row>
@@ -5813,51 +5093,42 @@
         <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>0.7239583333333334</v>
+        <v>139</v>
       </c>
       <c r="G63" t="n">
         <v>0.7239583333333334</v>
       </c>
       <c r="H63" t="n">
-        <v>88</v>
+        <v>0.7239583333333334</v>
       </c>
       <c r="I63" t="n">
-        <v>123</v>
+        <v>0.6422764227642277</v>
       </c>
       <c r="J63" t="n">
-        <v>0.6422764227642277</v>
+        <v>0.8977272727272727</v>
       </c>
       <c r="K63" t="n">
-        <v>0.8977272727272727</v>
+        <v>0.7488151658767773</v>
       </c>
       <c r="L63" t="n">
-        <v>0.7488151658767773</v>
+        <v>0.8695652173913043</v>
       </c>
       <c r="M63" t="n">
-        <v>104</v>
+        <v>0.5769230769230769</v>
       </c>
       <c r="N63" t="n">
-        <v>69</v>
+        <v>0.6936416184971097</v>
       </c>
       <c r="O63" t="n">
-        <v>0.8695652173913043</v>
+        <v>79</v>
       </c>
       <c r="P63" t="n">
-        <v>0.5769230769230769</v>
+        <v>9</v>
       </c>
       <c r="Q63" t="n">
-        <v>0.6936416184971097</v>
+        <v>44</v>
       </c>
       <c r="R63" t="n">
-        <v>79</v>
-      </c>
-      <c r="S63" t="n">
-        <v>9</v>
-      </c>
-      <c r="T63" t="n">
-        <v>44</v>
-      </c>
-      <c r="U63" t="n">
         <v>60</v>
       </c>
     </row>
@@ -5880,51 +5151,42 @@
         <v>0</v>
       </c>
       <c r="F64" t="n">
-        <v>0.6302083333333334</v>
+        <v>121</v>
       </c>
       <c r="G64" t="n">
         <v>0.6302083333333334</v>
       </c>
       <c r="H64" t="n">
-        <v>91</v>
+        <v>0.6302083333333334</v>
       </c>
       <c r="I64" t="n">
-        <v>142</v>
+        <v>0.5704225352112676</v>
       </c>
       <c r="J64" t="n">
-        <v>0.5704225352112676</v>
+        <v>0.8901098901098901</v>
       </c>
       <c r="K64" t="n">
-        <v>0.8901098901098901</v>
+        <v>0.6952789699570815</v>
       </c>
       <c r="L64" t="n">
-        <v>0.6952789699570815</v>
+        <v>0.8</v>
       </c>
       <c r="M64" t="n">
-        <v>101</v>
+        <v>0.3960396039603961</v>
       </c>
       <c r="N64" t="n">
-        <v>50</v>
+        <v>0.5298013245033113</v>
       </c>
       <c r="O64" t="n">
-        <v>0.8</v>
+        <v>81</v>
       </c>
       <c r="P64" t="n">
-        <v>0.3960396039603961</v>
+        <v>10</v>
       </c>
       <c r="Q64" t="n">
-        <v>0.5298013245033113</v>
+        <v>61</v>
       </c>
       <c r="R64" t="n">
-        <v>81</v>
-      </c>
-      <c r="S64" t="n">
-        <v>10</v>
-      </c>
-      <c r="T64" t="n">
-        <v>61</v>
-      </c>
-      <c r="U64" t="n">
         <v>40</v>
       </c>
     </row>
@@ -5947,51 +5209,42 @@
         <v>0</v>
       </c>
       <c r="F65" t="n">
-        <v>0.703125</v>
+        <v>135</v>
       </c>
       <c r="G65" t="n">
         <v>0.703125</v>
       </c>
       <c r="H65" t="n">
-        <v>95</v>
+        <v>0.703125</v>
       </c>
       <c r="I65" t="n">
-        <v>138</v>
+        <v>0.6376811594202898</v>
       </c>
       <c r="J65" t="n">
-        <v>0.6376811594202898</v>
+        <v>0.9263157894736842</v>
       </c>
       <c r="K65" t="n">
-        <v>0.9263157894736842</v>
+        <v>0.7553648068669527</v>
       </c>
       <c r="L65" t="n">
-        <v>0.7553648068669527</v>
+        <v>0.8703703703703703</v>
       </c>
       <c r="M65" t="n">
-        <v>97</v>
+        <v>0.4845360824742268</v>
       </c>
       <c r="N65" t="n">
-        <v>54</v>
+        <v>0.6225165562913907</v>
       </c>
       <c r="O65" t="n">
-        <v>0.8703703703703703</v>
+        <v>88</v>
       </c>
       <c r="P65" t="n">
-        <v>0.4845360824742268</v>
+        <v>7</v>
       </c>
       <c r="Q65" t="n">
-        <v>0.6225165562913907</v>
+        <v>50</v>
       </c>
       <c r="R65" t="n">
-        <v>88</v>
-      </c>
-      <c r="S65" t="n">
-        <v>7</v>
-      </c>
-      <c r="T65" t="n">
-        <v>50</v>
-      </c>
-      <c r="U65" t="n">
         <v>47</v>
       </c>
     </row>
@@ -6014,51 +5267,42 @@
         <v>0</v>
       </c>
       <c r="F66" t="n">
-        <v>0.8333333333333334</v>
+        <v>160</v>
       </c>
       <c r="G66" t="n">
         <v>0.8333333333333334</v>
       </c>
       <c r="H66" t="n">
-        <v>83</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="I66" t="n">
-        <v>101</v>
+        <v>0.7524752475247525</v>
       </c>
       <c r="J66" t="n">
-        <v>0.7524752475247525</v>
+        <v>0.9156626506024096</v>
       </c>
       <c r="K66" t="n">
-        <v>0.9156626506024096</v>
+        <v>0.826086956521739</v>
       </c>
       <c r="L66" t="n">
-        <v>0.826086956521739</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="M66" t="n">
-        <v>109</v>
+        <v>0.7706422018348624</v>
       </c>
       <c r="N66" t="n">
-        <v>91</v>
+        <v>0.84</v>
       </c>
       <c r="O66" t="n">
-        <v>0.9230769230769231</v>
+        <v>76</v>
       </c>
       <c r="P66" t="n">
-        <v>0.7706422018348624</v>
+        <v>7</v>
       </c>
       <c r="Q66" t="n">
-        <v>0.84</v>
+        <v>25</v>
       </c>
       <c r="R66" t="n">
-        <v>76</v>
-      </c>
-      <c r="S66" t="n">
-        <v>7</v>
-      </c>
-      <c r="T66" t="n">
-        <v>25</v>
-      </c>
-      <c r="U66" t="n">
         <v>84</v>
       </c>
     </row>
@@ -6081,51 +5325,42 @@
         <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>0.71875</v>
+        <v>138</v>
       </c>
       <c r="G67" t="n">
         <v>0.71875</v>
       </c>
       <c r="H67" t="n">
-        <v>92</v>
+        <v>0.71875</v>
       </c>
       <c r="I67" t="n">
-        <v>116</v>
+        <v>0.6637931034482759</v>
       </c>
       <c r="J67" t="n">
-        <v>0.6637931034482759</v>
+        <v>0.8369565217391305</v>
       </c>
       <c r="K67" t="n">
-        <v>0.8369565217391305</v>
+        <v>0.7403846153846154</v>
       </c>
       <c r="L67" t="n">
-        <v>0.7403846153846154</v>
+        <v>0.8026315789473685</v>
       </c>
       <c r="M67" t="n">
-        <v>100</v>
+        <v>0.61</v>
       </c>
       <c r="N67" t="n">
-        <v>76</v>
+        <v>0.6931818181818182</v>
       </c>
       <c r="O67" t="n">
-        <v>0.8026315789473685</v>
+        <v>77</v>
       </c>
       <c r="P67" t="n">
-        <v>0.61</v>
+        <v>15</v>
       </c>
       <c r="Q67" t="n">
-        <v>0.6931818181818182</v>
+        <v>39</v>
       </c>
       <c r="R67" t="n">
-        <v>77</v>
-      </c>
-      <c r="S67" t="n">
-        <v>15</v>
-      </c>
-      <c r="T67" t="n">
-        <v>39</v>
-      </c>
-      <c r="U67" t="n">
         <v>61</v>
       </c>
     </row>
@@ -6148,51 +5383,42 @@
         <v>0</v>
       </c>
       <c r="F68" t="n">
-        <v>0.75</v>
+        <v>144</v>
       </c>
       <c r="G68" t="n">
         <v>0.75</v>
       </c>
       <c r="H68" t="n">
-        <v>98</v>
+        <v>0.75</v>
       </c>
       <c r="I68" t="n">
-        <v>134</v>
+        <v>0.6865671641791045</v>
       </c>
       <c r="J68" t="n">
-        <v>0.6865671641791045</v>
+        <v>0.9387755102040817</v>
       </c>
       <c r="K68" t="n">
-        <v>0.9387755102040817</v>
+        <v>0.7931034482758622</v>
       </c>
       <c r="L68" t="n">
-        <v>0.7931034482758622</v>
+        <v>0.896551724137931</v>
       </c>
       <c r="M68" t="n">
-        <v>94</v>
+        <v>0.5531914893617021</v>
       </c>
       <c r="N68" t="n">
-        <v>58</v>
+        <v>0.6842105263157894</v>
       </c>
       <c r="O68" t="n">
-        <v>0.896551724137931</v>
+        <v>92</v>
       </c>
       <c r="P68" t="n">
-        <v>0.5531914893617021</v>
+        <v>6</v>
       </c>
       <c r="Q68" t="n">
-        <v>0.6842105263157894</v>
+        <v>42</v>
       </c>
       <c r="R68" t="n">
-        <v>92</v>
-      </c>
-      <c r="S68" t="n">
-        <v>6</v>
-      </c>
-      <c r="T68" t="n">
-        <v>42</v>
-      </c>
-      <c r="U68" t="n">
         <v>52</v>
       </c>
     </row>
@@ -6215,51 +5441,42 @@
         <v>0</v>
       </c>
       <c r="F69" t="n">
-        <v>0.8020833333333334</v>
+        <v>154</v>
       </c>
       <c r="G69" t="n">
         <v>0.8020833333333334</v>
       </c>
       <c r="H69" t="n">
-        <v>94</v>
+        <v>0.8020833333333334</v>
       </c>
       <c r="I69" t="n">
-        <v>126</v>
+        <v>0.7222222222222222</v>
       </c>
       <c r="J69" t="n">
-        <v>0.7222222222222222</v>
+        <v>0.9680851063829787</v>
       </c>
       <c r="K69" t="n">
-        <v>0.9680851063829787</v>
+        <v>0.8272727272727272</v>
       </c>
       <c r="L69" t="n">
-        <v>0.8272727272727272</v>
+        <v>0.9545454545454546</v>
       </c>
       <c r="M69" t="n">
-        <v>98</v>
+        <v>0.6428571428571429</v>
       </c>
       <c r="N69" t="n">
-        <v>66</v>
+        <v>0.7682926829268294</v>
       </c>
       <c r="O69" t="n">
-        <v>0.9545454545454546</v>
+        <v>91</v>
       </c>
       <c r="P69" t="n">
-        <v>0.6428571428571429</v>
+        <v>3</v>
       </c>
       <c r="Q69" t="n">
-        <v>0.7682926829268294</v>
+        <v>35</v>
       </c>
       <c r="R69" t="n">
-        <v>91</v>
-      </c>
-      <c r="S69" t="n">
-        <v>3</v>
-      </c>
-      <c r="T69" t="n">
-        <v>35</v>
-      </c>
-      <c r="U69" t="n">
         <v>63</v>
       </c>
     </row>
@@ -6282,53 +5499,44 @@
         <v>0</v>
       </c>
       <c r="F70" t="n">
-        <v>0.7708333333333334</v>
+        <v>148</v>
       </c>
       <c r="G70" t="n">
         <v>0.7708333333333334</v>
       </c>
       <c r="H70" t="n">
-        <v>83</v>
+        <v>0.7708333333333334</v>
       </c>
       <c r="I70" t="n">
-        <v>109</v>
+        <v>0.6788990825688074</v>
       </c>
       <c r="J70" t="n">
+        <v>0.8915662650602409</v>
+      </c>
+      <c r="K70" t="n">
+        <v>0.7708333333333334</v>
+      </c>
+      <c r="L70" t="n">
+        <v>0.8915662650602409</v>
+      </c>
+      <c r="M70" t="n">
         <v>0.6788990825688074</v>
       </c>
-      <c r="K70" t="n">
-        <v>0.8915662650602409</v>
-      </c>
-      <c r="L70" t="n">
+      <c r="N70" t="n">
         <v>0.7708333333333334</v>
       </c>
-      <c r="M70" t="n">
-        <v>109</v>
-      </c>
-      <c r="N70" t="n">
-        <v>83</v>
-      </c>
       <c r="O70" t="n">
-        <v>0.8915662650602409</v>
+        <v>74</v>
       </c>
       <c r="P70" t="n">
-        <v>0.6788990825688074</v>
+        <v>9</v>
       </c>
       <c r="Q70" t="n">
-        <v>0.7708333333333334</v>
+        <v>35</v>
       </c>
       <c r="R70" t="n">
         <v>74</v>
       </c>
-      <c r="S70" t="n">
-        <v>9</v>
-      </c>
-      <c r="T70" t="n">
-        <v>35</v>
-      </c>
-      <c r="U70" t="n">
-        <v>74</v>
-      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -6349,51 +5557,42 @@
         <v>0</v>
       </c>
       <c r="F71" t="n">
-        <v>0.6875</v>
+        <v>132</v>
       </c>
       <c r="G71" t="n">
         <v>0.6875</v>
       </c>
       <c r="H71" t="n">
-        <v>93</v>
+        <v>0.6875</v>
       </c>
       <c r="I71" t="n">
-        <v>137</v>
+        <v>0.6204379562043796</v>
       </c>
       <c r="J71" t="n">
-        <v>0.6204379562043796</v>
+        <v>0.9139784946236559</v>
       </c>
       <c r="K71" t="n">
-        <v>0.9139784946236559</v>
+        <v>0.7391304347826085</v>
       </c>
       <c r="L71" t="n">
-        <v>0.7391304347826085</v>
+        <v>0.8545454545454545</v>
       </c>
       <c r="M71" t="n">
-        <v>99</v>
+        <v>0.4747474747474748</v>
       </c>
       <c r="N71" t="n">
-        <v>55</v>
+        <v>0.6103896103896105</v>
       </c>
       <c r="O71" t="n">
-        <v>0.8545454545454545</v>
+        <v>85</v>
       </c>
       <c r="P71" t="n">
-        <v>0.4747474747474748</v>
+        <v>8</v>
       </c>
       <c r="Q71" t="n">
-        <v>0.6103896103896105</v>
+        <v>52</v>
       </c>
       <c r="R71" t="n">
-        <v>85</v>
-      </c>
-      <c r="S71" t="n">
-        <v>8</v>
-      </c>
-      <c r="T71" t="n">
-        <v>52</v>
-      </c>
-      <c r="U71" t="n">
         <v>47</v>
       </c>
     </row>
@@ -6416,51 +5615,42 @@
         <v>0</v>
       </c>
       <c r="F72" t="n">
-        <v>0.6770833333333334</v>
+        <v>130</v>
       </c>
       <c r="G72" t="n">
         <v>0.6770833333333334</v>
       </c>
       <c r="H72" t="n">
-        <v>101</v>
+        <v>0.6770833333333334</v>
       </c>
       <c r="I72" t="n">
-        <v>153</v>
+        <v>0.6274509803921569</v>
       </c>
       <c r="J72" t="n">
-        <v>0.6274509803921569</v>
+        <v>0.9504950495049505</v>
       </c>
       <c r="K72" t="n">
-        <v>0.9504950495049505</v>
+        <v>0.7559055118110235</v>
       </c>
       <c r="L72" t="n">
-        <v>0.7559055118110235</v>
+        <v>0.8717948717948718</v>
       </c>
       <c r="M72" t="n">
-        <v>91</v>
+        <v>0.3736263736263736</v>
       </c>
       <c r="N72" t="n">
-        <v>39</v>
+        <v>0.5230769230769231</v>
       </c>
       <c r="O72" t="n">
-        <v>0.8717948717948718</v>
+        <v>96</v>
       </c>
       <c r="P72" t="n">
-        <v>0.3736263736263736</v>
+        <v>5</v>
       </c>
       <c r="Q72" t="n">
-        <v>0.5230769230769231</v>
+        <v>57</v>
       </c>
       <c r="R72" t="n">
-        <v>96</v>
-      </c>
-      <c r="S72" t="n">
-        <v>5</v>
-      </c>
-      <c r="T72" t="n">
-        <v>57</v>
-      </c>
-      <c r="U72" t="n">
         <v>34</v>
       </c>
     </row>
@@ -6483,51 +5673,42 @@
         <v>0</v>
       </c>
       <c r="F73" t="n">
-        <v>0.7760416666666666</v>
+        <v>149</v>
       </c>
       <c r="G73" t="n">
         <v>0.7760416666666666</v>
       </c>
       <c r="H73" t="n">
-        <v>105</v>
+        <v>0.7760416666666666</v>
       </c>
       <c r="I73" t="n">
-        <v>134</v>
+        <v>0.7313432835820896</v>
       </c>
       <c r="J73" t="n">
-        <v>0.7313432835820896</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="K73" t="n">
-        <v>0.9333333333333333</v>
+        <v>0.8200836820083682</v>
       </c>
       <c r="L73" t="n">
-        <v>0.8200836820083682</v>
+        <v>0.8793103448275862</v>
       </c>
       <c r="M73" t="n">
-        <v>87</v>
+        <v>0.5862068965517241</v>
       </c>
       <c r="N73" t="n">
-        <v>58</v>
+        <v>0.7034482758620689</v>
       </c>
       <c r="O73" t="n">
-        <v>0.8793103448275862</v>
+        <v>98</v>
       </c>
       <c r="P73" t="n">
-        <v>0.5862068965517241</v>
+        <v>7</v>
       </c>
       <c r="Q73" t="n">
-        <v>0.7034482758620689</v>
+        <v>36</v>
       </c>
       <c r="R73" t="n">
-        <v>98</v>
-      </c>
-      <c r="S73" t="n">
-        <v>7</v>
-      </c>
-      <c r="T73" t="n">
-        <v>36</v>
-      </c>
-      <c r="U73" t="n">
         <v>51</v>
       </c>
     </row>
@@ -6550,51 +5731,42 @@
         <v>0</v>
       </c>
       <c r="F74" t="n">
-        <v>0.640625</v>
+        <v>123</v>
       </c>
       <c r="G74" t="n">
         <v>0.640625</v>
       </c>
       <c r="H74" t="n">
-        <v>84</v>
+        <v>0.640625</v>
       </c>
       <c r="I74" t="n">
-        <v>135</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="J74" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.8928571428571429</v>
       </c>
       <c r="K74" t="n">
-        <v>0.8928571428571429</v>
+        <v>0.684931506849315</v>
       </c>
       <c r="L74" t="n">
-        <v>0.684931506849315</v>
+        <v>0.8421052631578947</v>
       </c>
       <c r="M74" t="n">
-        <v>108</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="N74" t="n">
-        <v>57</v>
+        <v>0.5818181818181818</v>
       </c>
       <c r="O74" t="n">
-        <v>0.8421052631578947</v>
+        <v>75</v>
       </c>
       <c r="P74" t="n">
-        <v>0.4444444444444444</v>
+        <v>9</v>
       </c>
       <c r="Q74" t="n">
-        <v>0.5818181818181818</v>
+        <v>60</v>
       </c>
       <c r="R74" t="n">
-        <v>75</v>
-      </c>
-      <c r="S74" t="n">
-        <v>9</v>
-      </c>
-      <c r="T74" t="n">
-        <v>60</v>
-      </c>
-      <c r="U74" t="n">
         <v>48</v>
       </c>
     </row>
@@ -6617,51 +5789,42 @@
         <v>0</v>
       </c>
       <c r="F75" t="n">
-        <v>0.7864583333333334</v>
+        <v>151</v>
       </c>
       <c r="G75" t="n">
         <v>0.7864583333333334</v>
       </c>
       <c r="H75" t="n">
-        <v>99</v>
+        <v>0.7864583333333334</v>
       </c>
       <c r="I75" t="n">
-        <v>124</v>
+        <v>0.7338709677419355</v>
       </c>
       <c r="J75" t="n">
-        <v>0.7338709677419355</v>
+        <v>0.9191919191919192</v>
       </c>
       <c r="K75" t="n">
-        <v>0.9191919191919192</v>
+        <v>0.8161434977578476</v>
       </c>
       <c r="L75" t="n">
-        <v>0.8161434977578476</v>
+        <v>0.8823529411764706</v>
       </c>
       <c r="M75" t="n">
-        <v>93</v>
+        <v>0.6451612903225806</v>
       </c>
       <c r="N75" t="n">
-        <v>68</v>
+        <v>0.7453416149068324</v>
       </c>
       <c r="O75" t="n">
-        <v>0.8823529411764706</v>
+        <v>91</v>
       </c>
       <c r="P75" t="n">
-        <v>0.6451612903225806</v>
+        <v>8</v>
       </c>
       <c r="Q75" t="n">
-        <v>0.7453416149068324</v>
+        <v>33</v>
       </c>
       <c r="R75" t="n">
-        <v>91</v>
-      </c>
-      <c r="S75" t="n">
-        <v>8</v>
-      </c>
-      <c r="T75" t="n">
-        <v>33</v>
-      </c>
-      <c r="U75" t="n">
         <v>60</v>
       </c>
     </row>
@@ -6684,51 +5847,42 @@
         <v>0</v>
       </c>
       <c r="F76" t="n">
-        <v>0.8229166666666666</v>
+        <v>158</v>
       </c>
       <c r="G76" t="n">
         <v>0.8229166666666666</v>
       </c>
       <c r="H76" t="n">
-        <v>99</v>
+        <v>0.8229166666666666</v>
       </c>
       <c r="I76" t="n">
-        <v>119</v>
+        <v>0.773109243697479</v>
       </c>
       <c r="J76" t="n">
-        <v>0.773109243697479</v>
+        <v>0.9292929292929293</v>
       </c>
       <c r="K76" t="n">
-        <v>0.9292929292929293</v>
+        <v>0.8440366972477064</v>
       </c>
       <c r="L76" t="n">
-        <v>0.8440366972477064</v>
+        <v>0.9041095890410958</v>
       </c>
       <c r="M76" t="n">
-        <v>93</v>
+        <v>0.7096774193548387</v>
       </c>
       <c r="N76" t="n">
-        <v>73</v>
+        <v>0.7951807228915663</v>
       </c>
       <c r="O76" t="n">
-        <v>0.9041095890410958</v>
+        <v>92</v>
       </c>
       <c r="P76" t="n">
-        <v>0.7096774193548387</v>
+        <v>7</v>
       </c>
       <c r="Q76" t="n">
-        <v>0.7951807228915663</v>
+        <v>27</v>
       </c>
       <c r="R76" t="n">
-        <v>92</v>
-      </c>
-      <c r="S76" t="n">
-        <v>7</v>
-      </c>
-      <c r="T76" t="n">
-        <v>27</v>
-      </c>
-      <c r="U76" t="n">
         <v>66</v>
       </c>
     </row>
@@ -6751,51 +5905,42 @@
         <v>0</v>
       </c>
       <c r="F77" t="n">
-        <v>0.7135416666666666</v>
+        <v>137</v>
       </c>
       <c r="G77" t="n">
         <v>0.7135416666666666</v>
       </c>
       <c r="H77" t="n">
-        <v>97</v>
+        <v>0.7135416666666666</v>
       </c>
       <c r="I77" t="n">
-        <v>118</v>
+        <v>0.6779661016949152</v>
       </c>
       <c r="J77" t="n">
-        <v>0.6779661016949152</v>
+        <v>0.8247422680412371</v>
       </c>
       <c r="K77" t="n">
-        <v>0.8247422680412371</v>
+        <v>0.7441860465116279</v>
       </c>
       <c r="L77" t="n">
-        <v>0.7441860465116279</v>
+        <v>0.7702702702702703</v>
       </c>
       <c r="M77" t="n">
-        <v>95</v>
+        <v>0.6</v>
       </c>
       <c r="N77" t="n">
-        <v>74</v>
+        <v>0.6745562130177515</v>
       </c>
       <c r="O77" t="n">
-        <v>0.7702702702702703</v>
+        <v>80</v>
       </c>
       <c r="P77" t="n">
-        <v>0.6</v>
+        <v>17</v>
       </c>
       <c r="Q77" t="n">
-        <v>0.6745562130177515</v>
+        <v>38</v>
       </c>
       <c r="R77" t="n">
-        <v>80</v>
-      </c>
-      <c r="S77" t="n">
-        <v>17</v>
-      </c>
-      <c r="T77" t="n">
-        <v>38</v>
-      </c>
-      <c r="U77" t="n">
         <v>57</v>
       </c>
     </row>
@@ -6818,51 +5963,42 @@
         <v>0</v>
       </c>
       <c r="F78" t="n">
-        <v>0.8177083333333334</v>
+        <v>157</v>
       </c>
       <c r="G78" t="n">
         <v>0.8177083333333334</v>
       </c>
       <c r="H78" t="n">
-        <v>111</v>
+        <v>0.8177083333333334</v>
       </c>
       <c r="I78" t="n">
-        <v>132</v>
+        <v>0.7878787878787878</v>
       </c>
       <c r="J78" t="n">
-        <v>0.7878787878787878</v>
+        <v>0.9369369369369369</v>
       </c>
       <c r="K78" t="n">
-        <v>0.9369369369369369</v>
+        <v>0.8559670781893004</v>
       </c>
       <c r="L78" t="n">
-        <v>0.8559670781893004</v>
+        <v>0.8833333333333333</v>
       </c>
       <c r="M78" t="n">
-        <v>81</v>
+        <v>0.654320987654321</v>
       </c>
       <c r="N78" t="n">
-        <v>60</v>
+        <v>0.75177304964539</v>
       </c>
       <c r="O78" t="n">
-        <v>0.8833333333333333</v>
+        <v>104</v>
       </c>
       <c r="P78" t="n">
-        <v>0.654320987654321</v>
+        <v>7</v>
       </c>
       <c r="Q78" t="n">
-        <v>0.75177304964539</v>
+        <v>28</v>
       </c>
       <c r="R78" t="n">
-        <v>104</v>
-      </c>
-      <c r="S78" t="n">
-        <v>7</v>
-      </c>
-      <c r="T78" t="n">
-        <v>28</v>
-      </c>
-      <c r="U78" t="n">
         <v>53</v>
       </c>
     </row>
@@ -6885,51 +6021,42 @@
         <v>0</v>
       </c>
       <c r="F79" t="n">
-        <v>0.75</v>
+        <v>144</v>
       </c>
       <c r="G79" t="n">
         <v>0.75</v>
       </c>
       <c r="H79" t="n">
-        <v>94</v>
+        <v>0.75</v>
       </c>
       <c r="I79" t="n">
-        <v>132</v>
+        <v>0.6742424242424242</v>
       </c>
       <c r="J79" t="n">
-        <v>0.6742424242424242</v>
+        <v>0.9468085106382979</v>
       </c>
       <c r="K79" t="n">
-        <v>0.9468085106382979</v>
+        <v>0.7876106194690264</v>
       </c>
       <c r="L79" t="n">
-        <v>0.7876106194690264</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="M79" t="n">
-        <v>98</v>
+        <v>0.5612244897959183</v>
       </c>
       <c r="N79" t="n">
-        <v>60</v>
+        <v>0.6962025316455696</v>
       </c>
       <c r="O79" t="n">
-        <v>0.9166666666666666</v>
+        <v>89</v>
       </c>
       <c r="P79" t="n">
-        <v>0.5612244897959183</v>
+        <v>5</v>
       </c>
       <c r="Q79" t="n">
-        <v>0.6962025316455696</v>
+        <v>43</v>
       </c>
       <c r="R79" t="n">
-        <v>89</v>
-      </c>
-      <c r="S79" t="n">
-        <v>5</v>
-      </c>
-      <c r="T79" t="n">
-        <v>43</v>
-      </c>
-      <c r="U79" t="n">
         <v>55</v>
       </c>
     </row>
@@ -6952,51 +6079,42 @@
         <v>0</v>
       </c>
       <c r="F80" t="n">
-        <v>0.671875</v>
+        <v>129</v>
       </c>
       <c r="G80" t="n">
         <v>0.671875</v>
       </c>
       <c r="H80" t="n">
-        <v>87</v>
+        <v>0.671875</v>
       </c>
       <c r="I80" t="n">
-        <v>134</v>
+        <v>0.5895522388059702</v>
       </c>
       <c r="J80" t="n">
-        <v>0.5895522388059702</v>
+        <v>0.9080459770114943</v>
       </c>
       <c r="K80" t="n">
-        <v>0.9080459770114943</v>
+        <v>0.7149321266968326</v>
       </c>
       <c r="L80" t="n">
-        <v>0.7149321266968326</v>
+        <v>0.8620689655172413</v>
       </c>
       <c r="M80" t="n">
-        <v>105</v>
+        <v>0.4761904761904762</v>
       </c>
       <c r="N80" t="n">
-        <v>58</v>
+        <v>0.6134969325153374</v>
       </c>
       <c r="O80" t="n">
-        <v>0.8620689655172413</v>
+        <v>79</v>
       </c>
       <c r="P80" t="n">
-        <v>0.4761904761904762</v>
+        <v>8</v>
       </c>
       <c r="Q80" t="n">
-        <v>0.6134969325153374</v>
+        <v>55</v>
       </c>
       <c r="R80" t="n">
-        <v>79</v>
-      </c>
-      <c r="S80" t="n">
-        <v>8</v>
-      </c>
-      <c r="T80" t="n">
-        <v>55</v>
-      </c>
-      <c r="U80" t="n">
         <v>50</v>
       </c>
     </row>
@@ -7019,51 +6137,42 @@
         <v>0</v>
       </c>
       <c r="F81" t="n">
-        <v>0.6666666666666666</v>
+        <v>128</v>
       </c>
       <c r="G81" t="n">
         <v>0.6666666666666666</v>
       </c>
       <c r="H81" t="n">
-        <v>92</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="I81" t="n">
-        <v>128</v>
+        <v>0.609375</v>
       </c>
       <c r="J81" t="n">
-        <v>0.609375</v>
+        <v>0.8478260869565217</v>
       </c>
       <c r="K81" t="n">
-        <v>0.8478260869565217</v>
+        <v>0.709090909090909</v>
       </c>
       <c r="L81" t="n">
-        <v>0.709090909090909</v>
+        <v>0.78125</v>
       </c>
       <c r="M81" t="n">
-        <v>100</v>
+        <v>0.5</v>
       </c>
       <c r="N81" t="n">
-        <v>64</v>
+        <v>0.6097560975609756</v>
       </c>
       <c r="O81" t="n">
-        <v>0.78125</v>
+        <v>78</v>
       </c>
       <c r="P81" t="n">
-        <v>0.5</v>
+        <v>14</v>
       </c>
       <c r="Q81" t="n">
-        <v>0.6097560975609756</v>
+        <v>50</v>
       </c>
       <c r="R81" t="n">
-        <v>78</v>
-      </c>
-      <c r="S81" t="n">
-        <v>14</v>
-      </c>
-      <c r="T81" t="n">
-        <v>50</v>
-      </c>
-      <c r="U81" t="n">
         <v>50</v>
       </c>
     </row>
@@ -7086,51 +6195,42 @@
         <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>0.640625</v>
+        <v>123</v>
       </c>
       <c r="G82" t="n">
         <v>0.640625</v>
       </c>
       <c r="H82" t="n">
-        <v>84</v>
+        <v>0.640625</v>
       </c>
       <c r="I82" t="n">
-        <v>129</v>
+        <v>0.5581395348837209</v>
       </c>
       <c r="J82" t="n">
-        <v>0.5581395348837209</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="K82" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.676056338028169</v>
       </c>
       <c r="L82" t="n">
-        <v>0.676056338028169</v>
+        <v>0.8095238095238095</v>
       </c>
       <c r="M82" t="n">
-        <v>108</v>
+        <v>0.4722222222222222</v>
       </c>
       <c r="N82" t="n">
-        <v>63</v>
+        <v>0.5964912280701755</v>
       </c>
       <c r="O82" t="n">
-        <v>0.8095238095238095</v>
+        <v>72</v>
       </c>
       <c r="P82" t="n">
-        <v>0.4722222222222222</v>
+        <v>12</v>
       </c>
       <c r="Q82" t="n">
-        <v>0.5964912280701755</v>
+        <v>57</v>
       </c>
       <c r="R82" t="n">
-        <v>72</v>
-      </c>
-      <c r="S82" t="n">
-        <v>12</v>
-      </c>
-      <c r="T82" t="n">
-        <v>57</v>
-      </c>
-      <c r="U82" t="n">
         <v>51</v>
       </c>
     </row>
@@ -7153,51 +6253,42 @@
         <v>0</v>
       </c>
       <c r="F83" t="n">
-        <v>0.796875</v>
+        <v>153</v>
       </c>
       <c r="G83" t="n">
         <v>0.796875</v>
       </c>
       <c r="H83" t="n">
-        <v>94</v>
+        <v>0.796875</v>
       </c>
       <c r="I83" t="n">
-        <v>105</v>
+        <v>0.7619047619047619</v>
       </c>
       <c r="J83" t="n">
-        <v>0.7619047619047619</v>
+        <v>0.851063829787234</v>
       </c>
       <c r="K83" t="n">
-        <v>0.851063829787234</v>
+        <v>0.8040201005025126</v>
       </c>
       <c r="L83" t="n">
-        <v>0.8040201005025126</v>
+        <v>0.8390804597701149</v>
       </c>
       <c r="M83" t="n">
-        <v>98</v>
+        <v>0.7448979591836735</v>
       </c>
       <c r="N83" t="n">
-        <v>87</v>
+        <v>0.7891891891891891</v>
       </c>
       <c r="O83" t="n">
-        <v>0.8390804597701149</v>
+        <v>80</v>
       </c>
       <c r="P83" t="n">
-        <v>0.7448979591836735</v>
+        <v>14</v>
       </c>
       <c r="Q83" t="n">
-        <v>0.7891891891891891</v>
+        <v>25</v>
       </c>
       <c r="R83" t="n">
-        <v>80</v>
-      </c>
-      <c r="S83" t="n">
-        <v>14</v>
-      </c>
-      <c r="T83" t="n">
-        <v>25</v>
-      </c>
-      <c r="U83" t="n">
         <v>73</v>
       </c>
     </row>
@@ -7220,51 +6311,42 @@
         <v>0</v>
       </c>
       <c r="F84" t="n">
-        <v>0.8072916666666666</v>
+        <v>155</v>
       </c>
       <c r="G84" t="n">
         <v>0.8072916666666666</v>
       </c>
       <c r="H84" t="n">
-        <v>103</v>
+        <v>0.8072916666666666</v>
       </c>
       <c r="I84" t="n">
-        <v>118</v>
+        <v>0.7796610169491526</v>
       </c>
       <c r="J84" t="n">
-        <v>0.7796610169491526</v>
+        <v>0.8932038834951457</v>
       </c>
       <c r="K84" t="n">
-        <v>0.8932038834951457</v>
+        <v>0.8325791855203619</v>
       </c>
       <c r="L84" t="n">
-        <v>0.8325791855203619</v>
+        <v>0.8513513513513513</v>
       </c>
       <c r="M84" t="n">
-        <v>89</v>
+        <v>0.7078651685393258</v>
       </c>
       <c r="N84" t="n">
-        <v>74</v>
+        <v>0.7730061349693251</v>
       </c>
       <c r="O84" t="n">
-        <v>0.8513513513513513</v>
+        <v>92</v>
       </c>
       <c r="P84" t="n">
-        <v>0.7078651685393258</v>
+        <v>11</v>
       </c>
       <c r="Q84" t="n">
-        <v>0.7730061349693251</v>
+        <v>26</v>
       </c>
       <c r="R84" t="n">
-        <v>92</v>
-      </c>
-      <c r="S84" t="n">
-        <v>11</v>
-      </c>
-      <c r="T84" t="n">
-        <v>26</v>
-      </c>
-      <c r="U84" t="n">
         <v>63</v>
       </c>
     </row>
@@ -7287,51 +6369,42 @@
         <v>0</v>
       </c>
       <c r="F85" t="n">
-        <v>0.8072916666666666</v>
+        <v>155</v>
       </c>
       <c r="G85" t="n">
         <v>0.8072916666666666</v>
       </c>
       <c r="H85" t="n">
-        <v>107</v>
+        <v>0.8072916666666666</v>
       </c>
       <c r="I85" t="n">
-        <v>112</v>
+        <v>0.8125</v>
       </c>
       <c r="J85" t="n">
-        <v>0.8125</v>
+        <v>0.8504672897196262</v>
       </c>
       <c r="K85" t="n">
-        <v>0.8504672897196262</v>
+        <v>0.8310502283105022</v>
       </c>
       <c r="L85" t="n">
-        <v>0.8310502283105022</v>
+        <v>0.8</v>
       </c>
       <c r="M85" t="n">
-        <v>85</v>
+        <v>0.7529411764705882</v>
       </c>
       <c r="N85" t="n">
-        <v>80</v>
+        <v>0.7757575757575759</v>
       </c>
       <c r="O85" t="n">
-        <v>0.8</v>
+        <v>91</v>
       </c>
       <c r="P85" t="n">
-        <v>0.7529411764705882</v>
+        <v>16</v>
       </c>
       <c r="Q85" t="n">
-        <v>0.7757575757575759</v>
+        <v>21</v>
       </c>
       <c r="R85" t="n">
-        <v>91</v>
-      </c>
-      <c r="S85" t="n">
-        <v>16</v>
-      </c>
-      <c r="T85" t="n">
-        <v>21</v>
-      </c>
-      <c r="U85" t="n">
         <v>64</v>
       </c>
     </row>
@@ -7354,51 +6427,42 @@
         <v>0</v>
       </c>
       <c r="F86" t="n">
-        <v>0.765625</v>
+        <v>147</v>
       </c>
       <c r="G86" t="n">
         <v>0.765625</v>
       </c>
       <c r="H86" t="n">
-        <v>101</v>
+        <v>0.765625</v>
       </c>
       <c r="I86" t="n">
-        <v>134</v>
+        <v>0.7089552238805971</v>
       </c>
       <c r="J86" t="n">
-        <v>0.7089552238805971</v>
+        <v>0.9405940594059405</v>
       </c>
       <c r="K86" t="n">
-        <v>0.9405940594059405</v>
+        <v>0.8085106382978723</v>
       </c>
       <c r="L86" t="n">
-        <v>0.8085106382978723</v>
+        <v>0.896551724137931</v>
       </c>
       <c r="M86" t="n">
-        <v>91</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="N86" t="n">
-        <v>58</v>
+        <v>0.6979865771812079</v>
       </c>
       <c r="O86" t="n">
-        <v>0.896551724137931</v>
+        <v>95</v>
       </c>
       <c r="P86" t="n">
-        <v>0.5714285714285714</v>
+        <v>6</v>
       </c>
       <c r="Q86" t="n">
-        <v>0.6979865771812079</v>
+        <v>39</v>
       </c>
       <c r="R86" t="n">
-        <v>95</v>
-      </c>
-      <c r="S86" t="n">
-        <v>6</v>
-      </c>
-      <c r="T86" t="n">
-        <v>39</v>
-      </c>
-      <c r="U86" t="n">
         <v>52</v>
       </c>
     </row>
@@ -7421,51 +6485,42 @@
         <v>0</v>
       </c>
       <c r="F87" t="n">
-        <v>0.7916666666666666</v>
+        <v>152</v>
       </c>
       <c r="G87" t="n">
         <v>0.7916666666666666</v>
       </c>
       <c r="H87" t="n">
-        <v>97</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="I87" t="n">
-        <v>121</v>
+        <v>0.7355371900826446</v>
       </c>
       <c r="J87" t="n">
-        <v>0.7355371900826446</v>
+        <v>0.9175257731958762</v>
       </c>
       <c r="K87" t="n">
-        <v>0.9175257731958762</v>
+        <v>0.81651376146789</v>
       </c>
       <c r="L87" t="n">
-        <v>0.81651376146789</v>
+        <v>0.8873239436619719</v>
       </c>
       <c r="M87" t="n">
-        <v>95</v>
+        <v>0.6631578947368421</v>
       </c>
       <c r="N87" t="n">
-        <v>71</v>
+        <v>0.7590361445783133</v>
       </c>
       <c r="O87" t="n">
-        <v>0.8873239436619719</v>
+        <v>89</v>
       </c>
       <c r="P87" t="n">
-        <v>0.6631578947368421</v>
+        <v>8</v>
       </c>
       <c r="Q87" t="n">
-        <v>0.7590361445783133</v>
+        <v>32</v>
       </c>
       <c r="R87" t="n">
-        <v>89</v>
-      </c>
-      <c r="S87" t="n">
-        <v>8</v>
-      </c>
-      <c r="T87" t="n">
-        <v>32</v>
-      </c>
-      <c r="U87" t="n">
         <v>63</v>
       </c>
     </row>
@@ -7488,51 +6543,42 @@
         <v>0</v>
       </c>
       <c r="F88" t="n">
-        <v>0.8020833333333334</v>
+        <v>154</v>
       </c>
       <c r="G88" t="n">
         <v>0.8020833333333334</v>
       </c>
       <c r="H88" t="n">
-        <v>101</v>
+        <v>0.8020833333333334</v>
       </c>
       <c r="I88" t="n">
-        <v>127</v>
+        <v>0.7480314960629921</v>
       </c>
       <c r="J88" t="n">
-        <v>0.7480314960629921</v>
+        <v>0.9405940594059405</v>
       </c>
       <c r="K88" t="n">
-        <v>0.9405940594059405</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="L88" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.9076923076923077</v>
       </c>
       <c r="M88" t="n">
-        <v>91</v>
+        <v>0.6483516483516484</v>
       </c>
       <c r="N88" t="n">
-        <v>65</v>
+        <v>0.7564102564102564</v>
       </c>
       <c r="O88" t="n">
-        <v>0.9076923076923077</v>
+        <v>95</v>
       </c>
       <c r="P88" t="n">
-        <v>0.6483516483516484</v>
+        <v>6</v>
       </c>
       <c r="Q88" t="n">
-        <v>0.7564102564102564</v>
+        <v>32</v>
       </c>
       <c r="R88" t="n">
-        <v>95</v>
-      </c>
-      <c r="S88" t="n">
-        <v>6</v>
-      </c>
-      <c r="T88" t="n">
-        <v>32</v>
-      </c>
-      <c r="U88" t="n">
         <v>59</v>
       </c>
     </row>
@@ -7555,51 +6601,42 @@
         <v>0</v>
       </c>
       <c r="F89" t="n">
-        <v>0.7916666666666666</v>
+        <v>152</v>
       </c>
       <c r="G89" t="n">
         <v>0.7916666666666666</v>
       </c>
       <c r="H89" t="n">
-        <v>103</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="I89" t="n">
-        <v>133</v>
+        <v>0.7368421052631579</v>
       </c>
       <c r="J89" t="n">
-        <v>0.7368421052631579</v>
+        <v>0.9514563106796117</v>
       </c>
       <c r="K89" t="n">
-        <v>0.9514563106796117</v>
+        <v>0.8305084745762712</v>
       </c>
       <c r="L89" t="n">
-        <v>0.8305084745762712</v>
+        <v>0.9152542372881356</v>
       </c>
       <c r="M89" t="n">
-        <v>89</v>
+        <v>0.6067415730337079</v>
       </c>
       <c r="N89" t="n">
-        <v>59</v>
+        <v>0.7297297297297298</v>
       </c>
       <c r="O89" t="n">
-        <v>0.9152542372881356</v>
+        <v>98</v>
       </c>
       <c r="P89" t="n">
-        <v>0.6067415730337079</v>
+        <v>5</v>
       </c>
       <c r="Q89" t="n">
-        <v>0.7297297297297298</v>
+        <v>35</v>
       </c>
       <c r="R89" t="n">
-        <v>98</v>
-      </c>
-      <c r="S89" t="n">
-        <v>5</v>
-      </c>
-      <c r="T89" t="n">
-        <v>35</v>
-      </c>
-      <c r="U89" t="n">
         <v>54</v>
       </c>
     </row>
@@ -7622,51 +6659,42 @@
         <v>0</v>
       </c>
       <c r="F90" t="n">
-        <v>0.7916666666666666</v>
+        <v>152</v>
       </c>
       <c r="G90" t="n">
         <v>0.7916666666666666</v>
       </c>
       <c r="H90" t="n">
-        <v>100</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="I90" t="n">
-        <v>124</v>
+        <v>0.7419354838709677</v>
       </c>
       <c r="J90" t="n">
-        <v>0.7419354838709677</v>
+        <v>0.92</v>
       </c>
       <c r="K90" t="n">
-        <v>0.92</v>
+        <v>0.8214285714285714</v>
       </c>
       <c r="L90" t="n">
-        <v>0.8214285714285714</v>
+        <v>0.8823529411764706</v>
       </c>
       <c r="M90" t="n">
+        <v>0.6521739130434783</v>
+      </c>
+      <c r="N90" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="O90" t="n">
         <v>92</v>
       </c>
-      <c r="N90" t="n">
-        <v>68</v>
-      </c>
-      <c r="O90" t="n">
-        <v>0.8823529411764706</v>
-      </c>
       <c r="P90" t="n">
-        <v>0.6521739130434783</v>
+        <v>8</v>
       </c>
       <c r="Q90" t="n">
-        <v>0.75</v>
+        <v>32</v>
       </c>
       <c r="R90" t="n">
-        <v>92</v>
-      </c>
-      <c r="S90" t="n">
-        <v>8</v>
-      </c>
-      <c r="T90" t="n">
-        <v>32</v>
-      </c>
-      <c r="U90" t="n">
         <v>60</v>
       </c>
     </row>
@@ -7689,51 +6717,42 @@
         <v>0</v>
       </c>
       <c r="F91" t="n">
-        <v>0.7083333333333334</v>
+        <v>136</v>
       </c>
       <c r="G91" t="n">
         <v>0.7083333333333334</v>
       </c>
       <c r="H91" t="n">
-        <v>105</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="I91" t="n">
-        <v>129</v>
+        <v>0.689922480620155</v>
       </c>
       <c r="J91" t="n">
-        <v>0.689922480620155</v>
+        <v>0.8476190476190476</v>
       </c>
       <c r="K91" t="n">
-        <v>0.8476190476190476</v>
+        <v>0.7606837606837608</v>
       </c>
       <c r="L91" t="n">
-        <v>0.7606837606837608</v>
+        <v>0.746031746031746</v>
       </c>
       <c r="M91" t="n">
-        <v>87</v>
+        <v>0.5402298850574713</v>
       </c>
       <c r="N91" t="n">
-        <v>63</v>
+        <v>0.6266666666666666</v>
       </c>
       <c r="O91" t="n">
-        <v>0.746031746031746</v>
+        <v>89</v>
       </c>
       <c r="P91" t="n">
-        <v>0.5402298850574713</v>
+        <v>16</v>
       </c>
       <c r="Q91" t="n">
-        <v>0.6266666666666666</v>
+        <v>40</v>
       </c>
       <c r="R91" t="n">
-        <v>89</v>
-      </c>
-      <c r="S91" t="n">
-        <v>16</v>
-      </c>
-      <c r="T91" t="n">
-        <v>40</v>
-      </c>
-      <c r="U91" t="n">
         <v>47</v>
       </c>
     </row>
@@ -7756,51 +6775,42 @@
         <v>0</v>
       </c>
       <c r="F92" t="n">
-        <v>0.7604166666666666</v>
+        <v>146</v>
       </c>
       <c r="G92" t="n">
         <v>0.7604166666666666</v>
       </c>
       <c r="H92" t="n">
-        <v>106</v>
+        <v>0.7604166666666666</v>
       </c>
       <c r="I92" t="n">
-        <v>140</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="J92" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.9433962264150944</v>
       </c>
       <c r="K92" t="n">
-        <v>0.9433962264150944</v>
+        <v>0.8130081300813008</v>
       </c>
       <c r="L92" t="n">
-        <v>0.8130081300813008</v>
+        <v>0.8846153846153846</v>
       </c>
       <c r="M92" t="n">
-        <v>86</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="N92" t="n">
-        <v>52</v>
+        <v>0.6666666666666665</v>
       </c>
       <c r="O92" t="n">
-        <v>0.8846153846153846</v>
+        <v>100</v>
       </c>
       <c r="P92" t="n">
-        <v>0.5348837209302325</v>
+        <v>6</v>
       </c>
       <c r="Q92" t="n">
-        <v>0.6666666666666665</v>
+        <v>40</v>
       </c>
       <c r="R92" t="n">
-        <v>100</v>
-      </c>
-      <c r="S92" t="n">
-        <v>6</v>
-      </c>
-      <c r="T92" t="n">
-        <v>40</v>
-      </c>
-      <c r="U92" t="n">
         <v>46</v>
       </c>
     </row>
@@ -7823,51 +6833,42 @@
         <v>0</v>
       </c>
       <c r="F93" t="n">
-        <v>0.75</v>
+        <v>144</v>
       </c>
       <c r="G93" t="n">
         <v>0.75</v>
       </c>
       <c r="H93" t="n">
-        <v>103</v>
+        <v>0.75</v>
       </c>
       <c r="I93" t="n">
-        <v>119</v>
+        <v>0.7310924369747899</v>
       </c>
       <c r="J93" t="n">
-        <v>0.7310924369747899</v>
+        <v>0.8446601941747572</v>
       </c>
       <c r="K93" t="n">
-        <v>0.8446601941747572</v>
+        <v>0.7837837837837838</v>
       </c>
       <c r="L93" t="n">
-        <v>0.7837837837837838</v>
+        <v>0.7808219178082192</v>
       </c>
       <c r="M93" t="n">
-        <v>89</v>
+        <v>0.6404494382022472</v>
       </c>
       <c r="N93" t="n">
-        <v>73</v>
+        <v>0.7037037037037037</v>
       </c>
       <c r="O93" t="n">
-        <v>0.7808219178082192</v>
+        <v>87</v>
       </c>
       <c r="P93" t="n">
-        <v>0.6404494382022472</v>
+        <v>16</v>
       </c>
       <c r="Q93" t="n">
-        <v>0.7037037037037037</v>
+        <v>32</v>
       </c>
       <c r="R93" t="n">
-        <v>87</v>
-      </c>
-      <c r="S93" t="n">
-        <v>16</v>
-      </c>
-      <c r="T93" t="n">
-        <v>32</v>
-      </c>
-      <c r="U93" t="n">
         <v>57</v>
       </c>
     </row>
@@ -7890,51 +6891,42 @@
         <v>0</v>
       </c>
       <c r="F94" t="n">
-        <v>0.7708333333333334</v>
+        <v>148</v>
       </c>
       <c r="G94" t="n">
         <v>0.7708333333333334</v>
       </c>
       <c r="H94" t="n">
-        <v>104</v>
+        <v>0.7708333333333334</v>
       </c>
       <c r="I94" t="n">
-        <v>126</v>
+        <v>0.7380952380952381</v>
       </c>
       <c r="J94" t="n">
-        <v>0.7380952380952381</v>
+        <v>0.8942307692307693</v>
       </c>
       <c r="K94" t="n">
-        <v>0.8942307692307693</v>
+        <v>0.8086956521739131</v>
       </c>
       <c r="L94" t="n">
-        <v>0.8086956521739131</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="M94" t="n">
-        <v>88</v>
+        <v>0.625</v>
       </c>
       <c r="N94" t="n">
-        <v>66</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="O94" t="n">
-        <v>0.8333333333333334</v>
+        <v>93</v>
       </c>
       <c r="P94" t="n">
-        <v>0.625</v>
+        <v>11</v>
       </c>
       <c r="Q94" t="n">
-        <v>0.7142857142857143</v>
+        <v>33</v>
       </c>
       <c r="R94" t="n">
-        <v>93</v>
-      </c>
-      <c r="S94" t="n">
-        <v>11</v>
-      </c>
-      <c r="T94" t="n">
-        <v>33</v>
-      </c>
-      <c r="U94" t="n">
         <v>55</v>
       </c>
     </row>
@@ -7957,51 +6949,42 @@
         <v>0</v>
       </c>
       <c r="F95" t="n">
-        <v>0.7395833333333334</v>
+        <v>142</v>
       </c>
       <c r="G95" t="n">
         <v>0.7395833333333334</v>
       </c>
       <c r="H95" t="n">
-        <v>96</v>
+        <v>0.7395833333333334</v>
       </c>
       <c r="I95" t="n">
-        <v>120</v>
+        <v>0.6916666666666667</v>
       </c>
       <c r="J95" t="n">
-        <v>0.6916666666666667</v>
+        <v>0.8645833333333334</v>
       </c>
       <c r="K95" t="n">
-        <v>0.8645833333333334</v>
+        <v>0.7685185185185186</v>
       </c>
       <c r="L95" t="n">
-        <v>0.7685185185185186</v>
+        <v>0.8194444444444444</v>
       </c>
       <c r="M95" t="n">
-        <v>96</v>
+        <v>0.6145833333333334</v>
       </c>
       <c r="N95" t="n">
-        <v>72</v>
+        <v>0.7023809523809524</v>
       </c>
       <c r="O95" t="n">
-        <v>0.8194444444444444</v>
+        <v>83</v>
       </c>
       <c r="P95" t="n">
-        <v>0.6145833333333334</v>
+        <v>13</v>
       </c>
       <c r="Q95" t="n">
-        <v>0.7023809523809524</v>
+        <v>37</v>
       </c>
       <c r="R95" t="n">
-        <v>83</v>
-      </c>
-      <c r="S95" t="n">
-        <v>13</v>
-      </c>
-      <c r="T95" t="n">
-        <v>37</v>
-      </c>
-      <c r="U95" t="n">
         <v>59</v>
       </c>
     </row>
@@ -8024,51 +7007,42 @@
         <v>0</v>
       </c>
       <c r="F96" t="n">
-        <v>0.8333333333333334</v>
+        <v>160</v>
       </c>
       <c r="G96" t="n">
         <v>0.8333333333333334</v>
       </c>
       <c r="H96" t="n">
-        <v>94</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="I96" t="n">
-        <v>114</v>
+        <v>0.7719298245614035</v>
       </c>
       <c r="J96" t="n">
-        <v>0.7719298245614035</v>
+        <v>0.9361702127659575</v>
       </c>
       <c r="K96" t="n">
-        <v>0.9361702127659575</v>
+        <v>0.8461538461538461</v>
       </c>
       <c r="L96" t="n">
-        <v>0.8461538461538461</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="M96" t="n">
-        <v>98</v>
+        <v>0.7346938775510204</v>
       </c>
       <c r="N96" t="n">
-        <v>78</v>
+        <v>0.8181818181818182</v>
       </c>
       <c r="O96" t="n">
-        <v>0.9230769230769231</v>
+        <v>88</v>
       </c>
       <c r="P96" t="n">
-        <v>0.7346938775510204</v>
+        <v>6</v>
       </c>
       <c r="Q96" t="n">
-        <v>0.8181818181818182</v>
+        <v>26</v>
       </c>
       <c r="R96" t="n">
-        <v>88</v>
-      </c>
-      <c r="S96" t="n">
-        <v>6</v>
-      </c>
-      <c r="T96" t="n">
-        <v>26</v>
-      </c>
-      <c r="U96" t="n">
         <v>72</v>
       </c>
     </row>
@@ -8091,51 +7065,42 @@
         <v>0</v>
       </c>
       <c r="F97" t="n">
-        <v>0.8125</v>
+        <v>156</v>
       </c>
       <c r="G97" t="n">
         <v>0.8125</v>
       </c>
       <c r="H97" t="n">
-        <v>94</v>
+        <v>0.8125</v>
       </c>
       <c r="I97" t="n">
-        <v>112</v>
+        <v>0.7589285714285714</v>
       </c>
       <c r="J97" t="n">
-        <v>0.7589285714285714</v>
+        <v>0.9042553191489362</v>
       </c>
       <c r="K97" t="n">
-        <v>0.9042553191489362</v>
+        <v>0.8252427184466019</v>
       </c>
       <c r="L97" t="n">
-        <v>0.8252427184466019</v>
+        <v>0.8875</v>
       </c>
       <c r="M97" t="n">
-        <v>98</v>
+        <v>0.7244897959183674</v>
       </c>
       <c r="N97" t="n">
-        <v>80</v>
+        <v>0.797752808988764</v>
       </c>
       <c r="O97" t="n">
-        <v>0.8875</v>
+        <v>85</v>
       </c>
       <c r="P97" t="n">
-        <v>0.7244897959183674</v>
+        <v>9</v>
       </c>
       <c r="Q97" t="n">
-        <v>0.797752808988764</v>
+        <v>27</v>
       </c>
       <c r="R97" t="n">
-        <v>85</v>
-      </c>
-      <c r="S97" t="n">
-        <v>9</v>
-      </c>
-      <c r="T97" t="n">
-        <v>27</v>
-      </c>
-      <c r="U97" t="n">
         <v>71</v>
       </c>
     </row>
@@ -8158,51 +7123,42 @@
         <v>0</v>
       </c>
       <c r="F98" t="n">
-        <v>0.8489583333333334</v>
+        <v>163</v>
       </c>
       <c r="G98" t="n">
         <v>0.8489583333333334</v>
       </c>
       <c r="H98" t="n">
-        <v>90</v>
+        <v>0.8489583333333334</v>
       </c>
       <c r="I98" t="n">
-        <v>99</v>
+        <v>0.8080808080808081</v>
       </c>
       <c r="J98" t="n">
-        <v>0.8080808080808081</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="K98" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.8465608465608466</v>
       </c>
       <c r="L98" t="n">
-        <v>0.8465608465608466</v>
+        <v>0.8924731182795699</v>
       </c>
       <c r="M98" t="n">
-        <v>102</v>
+        <v>0.8137254901960784</v>
       </c>
       <c r="N98" t="n">
-        <v>93</v>
+        <v>0.8512820512820513</v>
       </c>
       <c r="O98" t="n">
-        <v>0.8924731182795699</v>
+        <v>80</v>
       </c>
       <c r="P98" t="n">
-        <v>0.8137254901960784</v>
+        <v>10</v>
       </c>
       <c r="Q98" t="n">
-        <v>0.8512820512820513</v>
+        <v>19</v>
       </c>
       <c r="R98" t="n">
-        <v>80</v>
-      </c>
-      <c r="S98" t="n">
-        <v>10</v>
-      </c>
-      <c r="T98" t="n">
-        <v>19</v>
-      </c>
-      <c r="U98" t="n">
         <v>83</v>
       </c>
     </row>
@@ -8225,51 +7181,42 @@
         <v>0</v>
       </c>
       <c r="F99" t="n">
-        <v>0.7760416666666666</v>
+        <v>149</v>
       </c>
       <c r="G99" t="n">
         <v>0.7760416666666666</v>
       </c>
       <c r="H99" t="n">
-        <v>101</v>
+        <v>0.7760416666666666</v>
       </c>
       <c r="I99" t="n">
-        <v>112</v>
+        <v>0.7589285714285714</v>
       </c>
       <c r="J99" t="n">
-        <v>0.7589285714285714</v>
+        <v>0.8415841584158416</v>
       </c>
       <c r="K99" t="n">
-        <v>0.8415841584158416</v>
+        <v>0.7981220657276994</v>
       </c>
       <c r="L99" t="n">
-        <v>0.7981220657276994</v>
+        <v>0.8</v>
       </c>
       <c r="M99" t="n">
-        <v>91</v>
+        <v>0.7032967032967034</v>
       </c>
       <c r="N99" t="n">
-        <v>80</v>
+        <v>0.7485380116959066</v>
       </c>
       <c r="O99" t="n">
-        <v>0.8</v>
+        <v>85</v>
       </c>
       <c r="P99" t="n">
-        <v>0.7032967032967034</v>
+        <v>16</v>
       </c>
       <c r="Q99" t="n">
-        <v>0.7485380116959066</v>
+        <v>27</v>
       </c>
       <c r="R99" t="n">
-        <v>85</v>
-      </c>
-      <c r="S99" t="n">
-        <v>16</v>
-      </c>
-      <c r="T99" t="n">
-        <v>27</v>
-      </c>
-      <c r="U99" t="n">
         <v>64</v>
       </c>
     </row>
@@ -8292,51 +7239,42 @@
         <v>0</v>
       </c>
       <c r="F100" t="n">
-        <v>0.8020833333333334</v>
+        <v>154</v>
       </c>
       <c r="G100" t="n">
         <v>0.8020833333333334</v>
       </c>
       <c r="H100" t="n">
-        <v>90</v>
+        <v>0.8020833333333334</v>
       </c>
       <c r="I100" t="n">
-        <v>110</v>
+        <v>0.7363636363636363</v>
       </c>
       <c r="J100" t="n">
-        <v>0.7363636363636363</v>
+        <v>0.9</v>
       </c>
       <c r="K100" t="n">
-        <v>0.9</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="L100" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8902439024390244</v>
       </c>
       <c r="M100" t="n">
-        <v>102</v>
+        <v>0.7156862745098039</v>
       </c>
       <c r="N100" t="n">
-        <v>82</v>
+        <v>0.7934782608695653</v>
       </c>
       <c r="O100" t="n">
-        <v>0.8902439024390244</v>
+        <v>81</v>
       </c>
       <c r="P100" t="n">
-        <v>0.7156862745098039</v>
+        <v>9</v>
       </c>
       <c r="Q100" t="n">
-        <v>0.7934782608695653</v>
+        <v>29</v>
       </c>
       <c r="R100" t="n">
-        <v>81</v>
-      </c>
-      <c r="S100" t="n">
-        <v>9</v>
-      </c>
-      <c r="T100" t="n">
-        <v>29</v>
-      </c>
-      <c r="U100" t="n">
         <v>73</v>
       </c>
     </row>
@@ -8359,51 +7297,42 @@
         <v>0</v>
       </c>
       <c r="F101" t="n">
-        <v>0.6614583333333334</v>
+        <v>127</v>
       </c>
       <c r="G101" t="n">
         <v>0.6614583333333334</v>
       </c>
       <c r="H101" t="n">
-        <v>98</v>
+        <v>0.6614583333333334</v>
       </c>
       <c r="I101" t="n">
-        <v>139</v>
+        <v>0.6187050359712231</v>
       </c>
       <c r="J101" t="n">
-        <v>0.6187050359712231</v>
+        <v>0.8775510204081632</v>
       </c>
       <c r="K101" t="n">
-        <v>0.8775510204081632</v>
+        <v>0.7257383966244726</v>
       </c>
       <c r="L101" t="n">
-        <v>0.7257383966244726</v>
+        <v>0.7735849056603774</v>
       </c>
       <c r="M101" t="n">
-        <v>94</v>
+        <v>0.4361702127659575</v>
       </c>
       <c r="N101" t="n">
+        <v>0.5578231292517007</v>
+      </c>
+      <c r="O101" t="n">
+        <v>86</v>
+      </c>
+      <c r="P101" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q101" t="n">
         <v>53</v>
       </c>
-      <c r="O101" t="n">
-        <v>0.7735849056603774</v>
-      </c>
-      <c r="P101" t="n">
-        <v>0.4361702127659575</v>
-      </c>
-      <c r="Q101" t="n">
-        <v>0.5578231292517007</v>
-      </c>
       <c r="R101" t="n">
-        <v>86</v>
-      </c>
-      <c r="S101" t="n">
-        <v>12</v>
-      </c>
-      <c r="T101" t="n">
-        <v>53</v>
-      </c>
-      <c r="U101" t="n">
         <v>41</v>
       </c>
     </row>
@@ -8424,19 +7353,19 @@
     <row r="1">
       <c r="B1" t="inlineStr">
         <is>
-          <t>predicted_0</t>
+          <t>pred_0</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>predicted_1</t>
+          <t>pred_1</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>actual_0</t>
+          <t>true_0</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -8449,7 +7378,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>actual_1</t>
+          <t>true_1</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -8481,22 +7410,22 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>actual_0_pred_0</t>
+          <t>true_0_pred_0</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>actual_0_pred_1</t>
+          <t>true_0_pred_1</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>actual_1_pred_0</t>
+          <t>true_1_pred_0</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>actual_1_pred_1</t>
+          <t>true_1_pred_1</t>
         </is>
       </c>
     </row>
